--- a/MR_UKBiobank/ContinuousData/gMR_dat.xlsx
+++ b/MR_UKBiobank/ContinuousData/gMR_dat.xlsx
@@ -6,23 +6,23 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="3148-0.0" r:id="rId3" sheetId="1"/>
-    <sheet name="30690-0.0" r:id="rId4" sheetId="2"/>
-    <sheet name="30780-0.0" r:id="rId5" sheetId="3"/>
-    <sheet name="30870-0.0" r:id="rId6" sheetId="4"/>
-    <sheet name="30630-0.0" r:id="rId7" sheetId="5"/>
-    <sheet name="30710-0.0" r:id="rId8" sheetId="6"/>
-    <sheet name="30750-0.0" r:id="rId9" sheetId="7"/>
-    <sheet name="30740-0.0" r:id="rId10" sheetId="8"/>
-    <sheet name="30640-0.0" r:id="rId11" sheetId="9"/>
-    <sheet name="30790-0.0" r:id="rId12" sheetId="10"/>
-    <sheet name="30760-0.0" r:id="rId13" sheetId="11"/>
+    <sheet name="eBMD" r:id="rId3" sheetId="1"/>
+    <sheet name="Cholesterol" r:id="rId4" sheetId="2"/>
+    <sheet name="LDL" r:id="rId5" sheetId="3"/>
+    <sheet name="HDL" r:id="rId6" sheetId="4"/>
+    <sheet name="Triglycerides" r:id="rId7" sheetId="5"/>
+    <sheet name="Apo-A" r:id="rId8" sheetId="6"/>
+    <sheet name="Apo-B" r:id="rId9" sheetId="7"/>
+    <sheet name="CRP" r:id="rId10" sheetId="8"/>
+    <sheet name="Lipoprotein" r:id="rId11" sheetId="9"/>
+    <sheet name="HbA1c" r:id="rId12" sheetId="10"/>
+    <sheet name="Glucose" r:id="rId13" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="55">
   <si>
     <t>SNP</t>
   </si>
@@ -90,9 +90,6 @@
     <t>exposure</t>
   </si>
   <si>
-    <t>pos</t>
-  </si>
-  <si>
     <t>action</t>
   </si>
   <si>
@@ -153,7 +150,7 @@
     <t>FALSE</t>
   </si>
   <si>
-    <t>3148-0.0</t>
+    <t>eBMD</t>
   </si>
   <si>
     <t>Sclerostin</t>
@@ -162,34 +159,34 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>30690-0.0</t>
+    <t>Cholesterol</t>
   </si>
   <si>
-    <t>30780-0.0</t>
+    <t>LDL</t>
   </si>
   <si>
-    <t>30870-0.0</t>
+    <t>HDL</t>
   </si>
   <si>
-    <t>30630-0.0</t>
+    <t>Triglycerides</t>
   </si>
   <si>
-    <t>30710-0.0</t>
+    <t>Apo-A</t>
   </si>
   <si>
-    <t>30750-0.0</t>
+    <t>Apo-B</t>
   </si>
   <si>
-    <t>30740-0.0</t>
+    <t>CRP</t>
   </si>
   <si>
-    <t>30640-0.0</t>
+    <t>Lipoprotein</t>
   </si>
   <si>
-    <t>30790-0.0</t>
+    <t>HbA1c</t>
   </si>
   <si>
-    <t>30760-0.0</t>
+    <t>Glucose</t>
   </si>
 </sst>
 </file>
@@ -314,28 +311,25 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
@@ -344,22 +338,22 @@
         <v>-0.038471659868774384</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5786</v>
+        <v>0.6624</v>
       </c>
       <c r="J2" t="n">
         <v>0.3860994853562147</v>
       </c>
       <c r="K2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" t="s">
         <v>42</v>
-      </c>
-      <c r="L2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" t="s">
-        <v>43</v>
       </c>
       <c r="O2" t="n">
         <v>0.005032008685759226</v>
@@ -371,7 +365,7 @@
         <v>214323.0</v>
       </c>
       <c r="R2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -383,42 +377,39 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X2" t="n">
-        <v>4.177427E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
@@ -427,22 +418,22 @@
         <v>0.034847248420357774</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3415</v>
+        <v>0.3171</v>
       </c>
       <c r="J3" t="n">
         <v>0.2865184791179668</v>
       </c>
       <c r="K3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" t="s">
         <v>42</v>
-      </c>
-      <c r="L3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" t="s">
-        <v>43</v>
       </c>
       <c r="O3" t="n">
         <v>0.00426676689582343</v>
@@ -454,7 +445,7 @@
         <v>214323.0</v>
       </c>
       <c r="R3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -466,42 +457,39 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
@@ -510,22 +498,22 @@
         <v>-0.04849768504033609</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6442</v>
+        <v>0.6699</v>
       </c>
       <c r="J4" t="n">
         <v>0.415977286618795</v>
       </c>
       <c r="K4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4" t="s">
         <v>42</v>
-      </c>
-      <c r="L4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" t="s">
-        <v>43</v>
       </c>
       <c r="O4" t="n">
         <v>0.0056440565000923934</v>
@@ -537,7 +525,7 @@
         <v>214323.0</v>
       </c>
       <c r="R4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -549,42 +537,39 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
@@ -593,22 +578,22 @@
         <v>0.07876189247277657</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0934</v>
+        <v>0.0882</v>
       </c>
       <c r="J5" t="n">
         <v>0.07108663092621884</v>
       </c>
       <c r="K5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" t="s">
         <v>42</v>
-      </c>
-      <c r="L5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" t="s">
-        <v>43</v>
       </c>
       <c r="O5" t="n">
         <v>0.006041547412946537</v>
@@ -620,7 +605,7 @@
         <v>214323.0</v>
       </c>
       <c r="R5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -632,42 +617,39 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
@@ -676,22 +658,22 @@
         <v>0.044220478704359564</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2995</v>
+        <v>0.2786</v>
       </c>
       <c r="J6" t="n">
         <v>0.25578216057072733</v>
       </c>
       <c r="K6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6" t="s">
         <v>42</v>
-      </c>
-      <c r="L6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6" t="s">
-        <v>43</v>
       </c>
       <c r="O6" t="n">
         <v>0.0042214907875013025</v>
@@ -703,7 +685,7 @@
         <v>214323.0</v>
       </c>
       <c r="R6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -715,42 +697,39 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
@@ -759,22 +738,22 @@
         <v>0.07689420144887592</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0944</v>
+        <v>0.0886</v>
       </c>
       <c r="J7" t="n">
         <v>0.07819506072610033</v>
       </c>
       <c r="K7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" t="s">
         <v>42</v>
-      </c>
-      <c r="L7" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7" t="s">
-        <v>43</v>
       </c>
       <c r="O7" t="n">
         <v>0.005808697524784639</v>
@@ -786,7 +765,7 @@
         <v>214323.0</v>
       </c>
       <c r="R7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -798,21 +777,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -903,64 +879,61 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>9.376095324920829E-4</v>
+        <v>-0.003806498929829664</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5786</v>
+        <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3863922286237116</v>
+        <v>0.38620572013419</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004513283631340966</v>
+        <v>0.004030170706335223</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8354286759956555</v>
+        <v>0.34491450873823615</v>
       </c>
       <c r="Q2" t="n">
-        <v>279796.0</v>
+        <v>351740.0</v>
       </c>
       <c r="R2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -972,78 +945,75 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X2" t="n">
-        <v>4.177427E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0019131810694534394</v>
+        <v>-0.0014198446925235276</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3415</v>
+        <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28564203919998854</v>
+        <v>0.2858190709046455</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0038215938171244743</v>
+        <v>0.0034149447045822763</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6166362568982493</v>
+        <v>0.6775757525992285</v>
       </c>
       <c r="Q3" t="n">
-        <v>279796.0</v>
+        <v>351740.0</v>
       </c>
       <c r="R3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -1055,78 +1025,75 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>3.616398040624297E-5</v>
+        <v>-3.551722631445365E-4</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6442</v>
+        <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4160906517605684</v>
+        <v>0.4160857451526696</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005060575174380083</v>
+        <v>0.004521483480922011</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9942981955107479</v>
+        <v>0.9373888907659219</v>
       </c>
       <c r="Q4" t="n">
-        <v>279796.0</v>
+        <v>351740.0</v>
       </c>
       <c r="R4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -1138,78 +1105,75 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0038123620445664193</v>
+        <v>0.00785809990604664</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0934</v>
+        <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07131803170881643</v>
+        <v>0.07149883436629328</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005407966097689434</v>
+        <v>0.0048267248778757245</v>
       </c>
       <c r="P5" t="n">
-        <v>0.48084005861270707</v>
+        <v>0.10351735565852002</v>
       </c>
       <c r="Q5" t="n">
-        <v>279796.0</v>
+        <v>351740.0</v>
       </c>
       <c r="R5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -1221,78 +1185,75 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-5.458104459678437E-4</v>
+        <v>0.0012062621455166355</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2995</v>
+        <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25526812391885517</v>
+        <v>0.2554244612497868</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0037831049092283955</v>
+        <v>0.0033802387277976366</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8852827996961675</v>
+        <v>0.7211990109745776</v>
       </c>
       <c r="Q6" t="n">
-        <v>279796.0</v>
+        <v>351740.0</v>
       </c>
       <c r="R6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -1304,78 +1265,75 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004508552375268015</v>
+        <v>0.003751338586334582</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0944</v>
+        <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07824450671203305</v>
+        <v>0.07842298288508558</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005205342617545942</v>
+        <v>0.0046465029527565085</v>
       </c>
       <c r="P7" t="n">
-        <v>0.38641445902047256</v>
+        <v>0.41946734120033724</v>
       </c>
       <c r="Q7" t="n">
-        <v>279796.0</v>
+        <v>351740.0</v>
       </c>
       <c r="R7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -1387,21 +1345,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1492,64 +1447,61 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.013129491545565919</v>
+        <v>-0.004721641140417785</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5786</v>
+        <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3861251463477502</v>
+        <v>0.38613733692172864</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0038313316283589225</v>
+        <v>0.004218628330923896</v>
       </c>
       <c r="P2" t="n">
-        <v>6.106480778575935E-4</v>
+        <v>0.2630402618716589</v>
       </c>
       <c r="Q2" t="n">
-        <v>322007.0</v>
+        <v>321778.0</v>
       </c>
       <c r="R2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -1561,78 +1513,75 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X2" t="n">
-        <v>4.177427E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.00572709788895107</v>
+        <v>0.002636794227644566</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3415</v>
+        <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28577484340402537</v>
+        <v>0.2857637874559479</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00324718178044719</v>
+        <v>0.0035752196943523527</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07778119882869097</v>
+        <v>0.46080702938192275</v>
       </c>
       <c r="Q3" t="n">
-        <v>322007.0</v>
+        <v>321778.0</v>
       </c>
       <c r="R3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -1644,78 +1593,75 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.010396504791458061</v>
+        <v>-0.004631981165334541</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6442</v>
+        <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.416068594782101</v>
+        <v>0.4160912181690482</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004299114963588015</v>
+        <v>0.004733978556172183</v>
       </c>
       <c r="P4" t="n">
-        <v>0.015594213886514784</v>
+        <v>0.3278504721819454</v>
       </c>
       <c r="Q4" t="n">
-        <v>322007.0</v>
+        <v>321778.0</v>
       </c>
       <c r="R4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -1727,78 +1673,75 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.00821656891497979</v>
+        <v>0.011016376469789898</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0934</v>
+        <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07140993829326692</v>
+        <v>0.07141880426878158</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004592260987779454</v>
+        <v>0.005055918249470786</v>
       </c>
       <c r="P5" t="n">
-        <v>0.07358020142279681</v>
+        <v>0.029339288827796225</v>
       </c>
       <c r="Q5" t="n">
-        <v>322007.0</v>
+        <v>321778.0</v>
       </c>
       <c r="R5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -1810,78 +1753,75 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.015981434408179444</v>
+        <v>0.004125945725551209</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2995</v>
+        <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2553391696453804</v>
+        <v>0.25532820764626546</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0032141728119288197</v>
+        <v>0.0035390065561924653</v>
       </c>
       <c r="P6" t="n">
-        <v>6.623932728278276E-7</v>
+        <v>0.24367654078858822</v>
       </c>
       <c r="Q6" t="n">
-        <v>322007.0</v>
+        <v>321778.0</v>
       </c>
       <c r="R6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -1893,78 +1833,75 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.003143760915569587</v>
+        <v>0.007260586600120222</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0944</v>
+        <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07826848484660272</v>
+        <v>0.0782837857156176</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004422106419502881</v>
+        <v>0.004868445652139601</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4771347442107754</v>
+        <v>0.13586898185601698</v>
       </c>
       <c r="Q7" t="n">
-        <v>322007.0</v>
+        <v>321778.0</v>
       </c>
       <c r="R7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -1976,21 +1913,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2081,28 +2015,25 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
@@ -2111,22 +2042,22 @@
         <v>-0.0019172710459829025</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5786</v>
+        <v>0.6624</v>
       </c>
       <c r="J2" t="n">
         <v>0.3861705061394606</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O2" t="n">
         <v>0.003954540639681136</v>
@@ -2138,7 +2069,7 @@
         <v>351741.0</v>
       </c>
       <c r="R2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -2150,42 +2081,39 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X2" t="n">
-        <v>4.177427E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
@@ -2194,22 +2122,22 @@
         <v>0.001735735786979485</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3415</v>
+        <v>0.3171</v>
       </c>
       <c r="J3" t="n">
         <v>0.285661893268058</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O3" t="n">
         <v>0.0033508730577333705</v>
@@ -2221,7 +2149,7 @@
         <v>351741.0</v>
       </c>
       <c r="R3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -2233,42 +2161,39 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
@@ -2277,22 +2202,22 @@
         <v>-0.0031614816960992783</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6442</v>
+        <v>0.6699</v>
       </c>
       <c r="J4" t="n">
         <v>0.41616132324636596</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O4" t="n">
         <v>0.004438654407112916</v>
@@ -2304,7 +2229,7 @@
         <v>351741.0</v>
       </c>
       <c r="R4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -2316,42 +2241,39 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
@@ -2360,22 +2282,22 @@
         <v>-0.002329592792198533</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0934</v>
+        <v>0.0882</v>
       </c>
       <c r="J5" t="n">
         <v>0.07142897757156544</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O5" t="n">
         <v>0.004738587670330936</v>
@@ -2387,7 +2309,7 @@
         <v>351741.0</v>
       </c>
       <c r="R5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -2399,42 +2321,39 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
@@ -2443,22 +2362,22 @@
         <v>5.966755594133536E-4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2995</v>
+        <v>0.2786</v>
       </c>
       <c r="J6" t="n">
         <v>0.2553981480691759</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O6" t="n">
         <v>0.0033171314234098203</v>
@@ -2470,7 +2389,7 @@
         <v>351741.0</v>
       </c>
       <c r="R6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -2482,42 +2401,39 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
@@ -2526,22 +2442,22 @@
         <v>-0.005226857326711219</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0944</v>
+        <v>0.0886</v>
       </c>
       <c r="J7" t="n">
         <v>0.07832183339445785</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O7" t="n">
         <v>0.004562198594239567</v>
@@ -2553,7 +2469,7 @@
         <v>351741.0</v>
       </c>
       <c r="R7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -2565,21 +2481,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2670,28 +2583,25 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
@@ -2700,22 +2610,22 @@
         <v>-0.0020197501904204085</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5786</v>
+        <v>0.6624</v>
       </c>
       <c r="J2" t="n">
         <v>0.3861759093110029</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O2" t="n">
         <v>0.004005742459224765</v>
@@ -2727,7 +2637,7 @@
         <v>351090.0</v>
       </c>
       <c r="R2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -2739,42 +2649,39 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X2" t="n">
-        <v>4.177427E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
@@ -2783,22 +2690,22 @@
         <v>0.002373165821656435</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3415</v>
+        <v>0.3171</v>
       </c>
       <c r="J3" t="n">
         <v>0.28565040303056194</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O3" t="n">
         <v>0.0033941758725285474</v>
@@ -2810,7 +2717,7 @@
         <v>351090.0</v>
       </c>
       <c r="R3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -2822,42 +2729,39 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
@@ -2866,22 +2770,22 @@
         <v>-0.004101141888513507</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6442</v>
+        <v>0.6699</v>
       </c>
       <c r="J4" t="n">
         <v>0.41617533965649833</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O4" t="n">
         <v>0.004496342158307523</v>
@@ -2893,7 +2797,7 @@
         <v>351090.0</v>
       </c>
       <c r="R4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -2905,42 +2809,39 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
@@ -2949,22 +2850,22 @@
         <v>-0.0012192712729850042</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0934</v>
+        <v>0.0882</v>
       </c>
       <c r="J5" t="n">
         <v>0.0714190093708166</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O5" t="n">
         <v>0.004800142531238532</v>
@@ -2976,7 +2877,7 @@
         <v>351090.0</v>
       </c>
       <c r="R5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -2988,42 +2889,39 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
@@ -3032,22 +2930,22 @@
         <v>0.0037081721462656576</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2995</v>
+        <v>0.2786</v>
       </c>
       <c r="J6" t="n">
         <v>0.25538750747671535</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O6" t="n">
         <v>0.0033600145803262815</v>
@@ -3059,7 +2957,7 @@
         <v>351090.0</v>
       </c>
       <c r="R6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -3071,42 +2969,39 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
@@ -3115,22 +3010,22 @@
         <v>-0.005209523007945031</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0944</v>
+        <v>0.0886</v>
       </c>
       <c r="J7" t="n">
         <v>0.07830898060326412</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O7" t="n">
         <v>0.004621506162320852</v>
@@ -3142,7 +3037,7 @@
         <v>351090.0</v>
       </c>
       <c r="R7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -3154,21 +3049,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3259,64 +3151,61 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.01430583472052661</v>
+        <v>0.013129491545565919</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5786</v>
+        <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38617649067297954</v>
+        <v>0.3861251463477502</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003942850180592509</v>
+        <v>0.0038313316283589225</v>
       </c>
       <c r="P2" t="n">
-        <v>2.853364346669936E-4</v>
+        <v>6.106480778575935E-4</v>
       </c>
       <c r="Q2" t="n">
-        <v>351452.0</v>
+        <v>322007.0</v>
       </c>
       <c r="R2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -3328,78 +3217,75 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X2" t="n">
-        <v>4.177427E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0102744813888558</v>
+        <v>-0.00572709788895107</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3415</v>
+        <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28566063075469766</v>
+        <v>0.28577484340402537</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0033409205607358764</v>
+        <v>0.00324718178044719</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0021027572696300178</v>
+        <v>0.07778119882869097</v>
       </c>
       <c r="Q3" t="n">
-        <v>351452.0</v>
+        <v>322007.0</v>
       </c>
       <c r="R3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -3411,78 +3297,75 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.01494086826170413</v>
+        <v>0.010396504791458061</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6442</v>
+        <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161777426220366</v>
+        <v>0.416068594782101</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004425804551481263</v>
+        <v>0.004299114963588015</v>
       </c>
       <c r="P4" t="n">
-        <v>7.359502464391945E-4</v>
+        <v>0.015594213886514784</v>
       </c>
       <c r="Q4" t="n">
-        <v>351452.0</v>
+        <v>322007.0</v>
       </c>
       <c r="R4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -3494,78 +3377,75 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.010155778356459064</v>
+        <v>-0.00821656891497979</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0934</v>
+        <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07142938438250458</v>
+        <v>0.07140993829326692</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004724536333968606</v>
+        <v>0.004592260987779454</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03158897235278783</v>
+        <v>0.07358020142279681</v>
       </c>
       <c r="Q5" t="n">
-        <v>351452.0</v>
+        <v>322007.0</v>
       </c>
       <c r="R5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -3577,78 +3457,75 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.014547005081399464</v>
+        <v>-0.015981434408179444</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2995</v>
+        <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2554118343329957</v>
+        <v>0.2553391696453804</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003307235731756658</v>
+        <v>0.0032141728119288197</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0901405269863E-5</v>
+        <v>6.623932728278276E-7</v>
       </c>
       <c r="Q6" t="n">
-        <v>351452.0</v>
+        <v>322007.0</v>
       </c>
       <c r="R6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -3660,78 +3537,75 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004577178384059716</v>
+        <v>-0.003143760915569587</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0944</v>
+        <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07833359889828483</v>
+        <v>0.07826848484660272</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004548434774068563</v>
+        <v>0.004422106419502881</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3142626196608318</v>
+        <v>0.4771347442107754</v>
       </c>
       <c r="Q7" t="n">
-        <v>351452.0</v>
+        <v>322007.0</v>
       </c>
       <c r="R7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -3743,21 +3617,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3848,64 +3719,61 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.010998553728101617</v>
+        <v>-0.01430583472052661</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5786</v>
+        <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3861413501714414</v>
+        <v>0.38617649067297954</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0038981392682733936</v>
+        <v>0.003942850180592509</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004780434618875145</v>
+        <v>2.853364346669936E-4</v>
       </c>
       <c r="Q2" t="n">
-        <v>320226.0</v>
+        <v>351452.0</v>
       </c>
       <c r="R2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -3917,78 +3785,75 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X2" t="n">
-        <v>4.177427E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.00181633037528572</v>
+        <v>0.0102744813888558</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3415</v>
+        <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2857747340940461</v>
+        <v>0.28566063075469766</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0033036372761839176</v>
+        <v>0.0033409205607358764</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5824588937437769</v>
+        <v>0.0021027572696300178</v>
       </c>
       <c r="Q3" t="n">
-        <v>320226.0</v>
+        <v>351452.0</v>
       </c>
       <c r="R3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -4000,78 +3865,75 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007021690933490242</v>
+        <v>-0.01494086826170413</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6442</v>
+        <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41605928313128854</v>
+        <v>0.4161777426220366</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004373662814238708</v>
+        <v>0.004425804551481263</v>
       </c>
       <c r="P4" t="n">
-        <v>0.10839609774250065</v>
+        <v>7.359502464391945E-4</v>
       </c>
       <c r="Q4" t="n">
-        <v>320226.0</v>
+        <v>351452.0</v>
       </c>
       <c r="R4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -4083,78 +3945,75 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.00533539630898254</v>
+        <v>0.010155778356459064</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0934</v>
+        <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0714276792015639</v>
+        <v>0.07142938438250458</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0046716005000663795</v>
+        <v>0.004724536333968606</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2534167455661521</v>
+        <v>0.03158897235278783</v>
       </c>
       <c r="Q5" t="n">
-        <v>320226.0</v>
+        <v>351452.0</v>
       </c>
       <c r="R5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -4166,78 +4025,75 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.012450793686876604</v>
+        <v>0.014547005081399464</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2995</v>
+        <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2553415400373486</v>
+        <v>0.2554118343329957</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003270096585190361</v>
+        <v>0.003307235731756658</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4042207644442674E-4</v>
+        <v>1.0901405269863E-5</v>
       </c>
       <c r="Q6" t="n">
-        <v>320226.0</v>
+        <v>351452.0</v>
       </c>
       <c r="R6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -4249,78 +4105,75 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0424717751185207E-4</v>
+        <v>0.004577178384059716</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0944</v>
+        <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07826972200883127</v>
+        <v>0.07833359889828483</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004498926266961102</v>
+        <v>0.004548434774068563</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9637892312570266</v>
+        <v>0.3142626196608318</v>
       </c>
       <c r="Q7" t="n">
-        <v>320226.0</v>
+        <v>351452.0</v>
       </c>
       <c r="R7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -4332,21 +4185,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4437,64 +4287,61 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0038690963135752203</v>
+        <v>0.010998553728101617</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5786</v>
+        <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38620414559441557</v>
+        <v>0.3861413501714414</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004023844871261818</v>
+        <v>0.0038981392682733936</v>
       </c>
       <c r="P2" t="n">
-        <v>0.33628032218182935</v>
+        <v>0.004780434618875145</v>
       </c>
       <c r="Q2" t="n">
-        <v>350975.0</v>
+        <v>320226.0</v>
       </c>
       <c r="R2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -4506,78 +4353,75 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X2" t="n">
-        <v>4.177427E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002376815526289553</v>
+        <v>-0.00181633037528572</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3415</v>
+        <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28563287983474606</v>
+        <v>0.2857747340940461</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0034091825158449026</v>
+        <v>0.0033036372761839176</v>
       </c>
       <c r="P3" t="n">
-        <v>0.485690310790185</v>
+        <v>0.5824588937437769</v>
       </c>
       <c r="Q3" t="n">
-        <v>350975.0</v>
+        <v>320226.0</v>
       </c>
       <c r="R3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -4589,78 +4433,75 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0017787381903987731</v>
+        <v>0.007021690933490242</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6442</v>
+        <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161720920293468</v>
+        <v>0.41605928313128854</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004516207786443735</v>
+        <v>0.004373662814238708</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6936871619733798</v>
+        <v>0.10839609774250065</v>
       </c>
       <c r="Q4" t="n">
-        <v>350975.0</v>
+        <v>320226.0</v>
       </c>
       <c r="R4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -4672,78 +4513,75 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0014018026608490608</v>
+        <v>-0.00533539630898254</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0934</v>
+        <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07144098582520123</v>
+        <v>0.0714276792015639</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004820797855989508</v>
+        <v>0.0046716005000663795</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7712179994417725</v>
+        <v>0.2534167455661521</v>
       </c>
       <c r="Q5" t="n">
-        <v>350975.0</v>
+        <v>320226.0</v>
       </c>
       <c r="R5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -4755,78 +4593,75 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>5.780395479382013E-4</v>
+        <v>-0.012450793686876604</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2995</v>
+        <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2553714652040744</v>
+        <v>0.2553415400373486</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0033749057604561977</v>
+        <v>0.003270096585190361</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8640070385333598</v>
+        <v>1.4042207644442674E-4</v>
       </c>
       <c r="Q6" t="n">
-        <v>350975.0</v>
+        <v>320226.0</v>
       </c>
       <c r="R6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -4838,78 +4673,75 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001989965957543396</v>
+        <v>-2.0424717751185207E-4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0944</v>
+        <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0783275162048579</v>
+        <v>0.07826972200883127</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004641547433226485</v>
+        <v>0.004498926266961102</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6681207217510524</v>
+        <v>0.9637892312570266</v>
       </c>
       <c r="Q7" t="n">
-        <v>350975.0</v>
+        <v>320226.0</v>
       </c>
       <c r="R7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -4921,21 +4753,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5026,64 +4855,61 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.003806498929829664</v>
+        <v>-0.005889793107628681</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5786</v>
+        <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38620572013419</v>
+        <v>0.3862298201057596</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004030170706335223</v>
+        <v>0.004026882370114043</v>
       </c>
       <c r="P2" t="n">
-        <v>0.34491450873823615</v>
+        <v>0.14357266506237049</v>
       </c>
       <c r="Q2" t="n">
-        <v>351740.0</v>
+        <v>350039.0</v>
       </c>
       <c r="R2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -5095,78 +4921,75 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X2" t="n">
-        <v>4.177427E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0014198446925235276</v>
+        <v>0.004221351128715135</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3415</v>
+        <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2858190709046455</v>
+        <v>0.2856553126937284</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0034149447045822763</v>
+        <v>0.003411522418330872</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6775757525992285</v>
+        <v>0.21594670513699074</v>
       </c>
       <c r="Q3" t="n">
-        <v>351740.0</v>
+        <v>350039.0</v>
       </c>
       <c r="R3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -5178,78 +5001,75 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.551722631445365E-4</v>
+        <v>-0.007410104487496083</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6442</v>
+        <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4160857451526696</v>
+        <v>0.4162064798493882</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004521483480922011</v>
+        <v>0.00451998730545515</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9373888907659219</v>
+        <v>0.10112916287179191</v>
       </c>
       <c r="Q4" t="n">
-        <v>351740.0</v>
+        <v>350039.0</v>
       </c>
       <c r="R4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -5261,78 +5081,75 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00785809990604664</v>
+        <v>0.0024276003051405875</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0934</v>
+        <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07149883436629328</v>
+        <v>0.07146203708729598</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0048267248778757245</v>
+        <v>0.004823466937374072</v>
       </c>
       <c r="P5" t="n">
-        <v>0.10351735565852002</v>
+        <v>0.6147610581965657</v>
       </c>
       <c r="Q5" t="n">
-        <v>351740.0</v>
+        <v>350039.0</v>
       </c>
       <c r="R5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -5344,78 +5161,75 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0012062621455166355</v>
+        <v>0.006657255403560866</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2995</v>
+        <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2554244612497868</v>
+        <v>0.2554143966815126</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0033802387277976366</v>
+        <v>0.003377170083501139</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7211990109745776</v>
+        <v>0.04869577331431327</v>
       </c>
       <c r="Q6" t="n">
-        <v>351740.0</v>
+        <v>350039.0</v>
       </c>
       <c r="R6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -5427,78 +5241,75 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003751338586334582</v>
+        <v>-0.002390568292555957</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0944</v>
+        <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07842298288508558</v>
+        <v>0.07836126831581623</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0046465029527565085</v>
+        <v>0.0046438607168498595</v>
       </c>
       <c r="P7" t="n">
-        <v>0.41946734120033724</v>
+        <v>0.6067068360032342</v>
       </c>
       <c r="Q7" t="n">
-        <v>351740.0</v>
+        <v>350039.0</v>
       </c>
       <c r="R7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -5510,21 +5321,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5615,64 +5423,61 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.004721641140417785</v>
+        <v>-0.0038690963135752203</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5786</v>
+        <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38613733692172864</v>
+        <v>0.38620414559441557</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004218628330923896</v>
+        <v>0.004023844871261818</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2630402618716589</v>
+        <v>0.33628032218182935</v>
       </c>
       <c r="Q2" t="n">
-        <v>321778.0</v>
+        <v>350975.0</v>
       </c>
       <c r="R2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -5684,78 +5489,75 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X2" t="n">
-        <v>4.177427E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002636794227644566</v>
+        <v>0.002376815526289553</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3415</v>
+        <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2857637874559479</v>
+        <v>0.28563287983474606</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0035752196943523527</v>
+        <v>0.0034091825158449026</v>
       </c>
       <c r="P3" t="n">
-        <v>0.46080702938192275</v>
+        <v>0.485690310790185</v>
       </c>
       <c r="Q3" t="n">
-        <v>321778.0</v>
+        <v>350975.0</v>
       </c>
       <c r="R3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -5767,78 +5569,75 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.004631981165334541</v>
+        <v>0.0017787381903987731</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6442</v>
+        <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4160912181690482</v>
+        <v>0.4161720920293468</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004733978556172183</v>
+        <v>0.004516207786443735</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3278504721819454</v>
+        <v>0.6936871619733798</v>
       </c>
       <c r="Q4" t="n">
-        <v>321778.0</v>
+        <v>350975.0</v>
       </c>
       <c r="R4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -5850,78 +5649,75 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.011016376469789898</v>
+        <v>0.0014018026608490608</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0934</v>
+        <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07141880426878158</v>
+        <v>0.07144098582520123</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005055918249470786</v>
+        <v>0.004820797855989508</v>
       </c>
       <c r="P5" t="n">
-        <v>0.029339288827796225</v>
+        <v>0.7712179994417725</v>
       </c>
       <c r="Q5" t="n">
-        <v>321778.0</v>
+        <v>350975.0</v>
       </c>
       <c r="R5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -5933,78 +5729,75 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004125945725551209</v>
+        <v>5.780395479382013E-4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2995</v>
+        <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25532820764626546</v>
+        <v>0.2553714652040744</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0035390065561924653</v>
+        <v>0.0033749057604561977</v>
       </c>
       <c r="P6" t="n">
-        <v>0.24367654078858822</v>
+        <v>0.8640070385333598</v>
       </c>
       <c r="Q6" t="n">
-        <v>321778.0</v>
+        <v>350975.0</v>
       </c>
       <c r="R6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -6016,78 +5809,75 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007260586600120222</v>
+        <v>0.001989965957543396</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0944</v>
+        <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0782837857156176</v>
+        <v>0.0783275162048579</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004868445652139601</v>
+        <v>0.004641547433226485</v>
       </c>
       <c r="P7" t="n">
-        <v>0.13586898185601698</v>
+        <v>0.6681207217510524</v>
       </c>
       <c r="Q7" t="n">
-        <v>321778.0</v>
+        <v>350975.0</v>
       </c>
       <c r="R7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -6099,21 +5889,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -6204,64 +5991,61 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.005889793107628681</v>
+        <v>9.376095324920829E-4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5786</v>
+        <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3862298201057596</v>
+        <v>0.3863922286237116</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004026882370114043</v>
+        <v>0.004513283631340966</v>
       </c>
       <c r="P2" t="n">
-        <v>0.14357266506237049</v>
+        <v>0.8354286759956555</v>
       </c>
       <c r="Q2" t="n">
-        <v>350039.0</v>
+        <v>279796.0</v>
       </c>
       <c r="R2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -6273,78 +6057,75 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X2" t="n">
-        <v>4.177427E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004221351128715135</v>
+        <v>-0.0019131810694534394</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3415</v>
+        <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2856553126937284</v>
+        <v>0.28564203919998854</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003411522418330872</v>
+        <v>0.0038215938171244743</v>
       </c>
       <c r="P3" t="n">
-        <v>0.21594670513699074</v>
+        <v>0.6166362568982493</v>
       </c>
       <c r="Q3" t="n">
-        <v>350039.0</v>
+        <v>279796.0</v>
       </c>
       <c r="R3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -6356,78 +6137,75 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.007410104487496083</v>
+        <v>3.616398040624297E-5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6442</v>
+        <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4162064798493882</v>
+        <v>0.4160906517605684</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00451998730545515</v>
+        <v>0.005060575174380083</v>
       </c>
       <c r="P4" t="n">
-        <v>0.10112916287179191</v>
+        <v>0.9942981955107479</v>
       </c>
       <c r="Q4" t="n">
-        <v>350039.0</v>
+        <v>279796.0</v>
       </c>
       <c r="R4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -6439,78 +6217,75 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0024276003051405875</v>
+        <v>-0.0038123620445664193</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0934</v>
+        <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07146203708729598</v>
+        <v>0.07131803170881643</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004823466937374072</v>
+        <v>0.005407966097689434</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6147610581965657</v>
+        <v>0.48084005861270707</v>
       </c>
       <c r="Q5" t="n">
-        <v>350039.0</v>
+        <v>279796.0</v>
       </c>
       <c r="R5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -6522,78 +6297,75 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006657255403560866</v>
+        <v>-5.458104459678437E-4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2995</v>
+        <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2554143966815126</v>
+        <v>0.25526812391885517</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003377170083501139</v>
+        <v>0.0037831049092283955</v>
       </c>
       <c r="P6" t="n">
-        <v>0.04869577331431327</v>
+        <v>0.8852827996961675</v>
       </c>
       <c r="Q6" t="n">
-        <v>350039.0</v>
+        <v>279796.0</v>
       </c>
       <c r="R6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -6605,78 +6377,75 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.002390568292555957</v>
+        <v>0.004508552375268015</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0944</v>
+        <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07836126831581623</v>
+        <v>0.07824450671203305</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0046438607168498595</v>
+        <v>0.005205342617545942</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6067068360032342</v>
+        <v>0.38641445902047256</v>
       </c>
       <c r="Q7" t="n">
-        <v>350039.0</v>
+        <v>279796.0</v>
       </c>
       <c r="R7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -6688,21 +6457,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>

--- a/MR_UKBiobank/ContinuousData/gMR_dat.xlsx
+++ b/MR_UKBiobank/ContinuousData/gMR_dat.xlsx
@@ -412,7 +412,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>0.034847248420357774</v>
@@ -454,7 +454,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -572,7 +572,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>0.07876189247277657</v>
@@ -614,7 +614,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -732,7 +732,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>0.07689420144887592</v>
@@ -774,7 +774,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -980,7 +980,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>-0.0014198446925235276</v>
@@ -1022,7 +1022,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -1140,7 +1140,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>0.00785809990604664</v>
@@ -1182,7 +1182,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -1300,7 +1300,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>0.003751338586334582</v>
@@ -1342,7 +1342,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -1548,7 +1548,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>0.002636794227644566</v>
@@ -1590,7 +1590,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -1708,7 +1708,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>0.011016376469789898</v>
@@ -1750,7 +1750,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -1868,7 +1868,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>0.007260586600120222</v>
@@ -1910,7 +1910,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -2116,7 +2116,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>0.001735735786979485</v>
@@ -2158,7 +2158,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -2276,7 +2276,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>-0.002329592792198533</v>
@@ -2318,7 +2318,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -2436,7 +2436,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>-0.005226857326711219</v>
@@ -2478,7 +2478,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -2684,7 +2684,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>0.002373165821656435</v>
@@ -2726,7 +2726,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -2844,7 +2844,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>-0.0012192712729850042</v>
@@ -2886,7 +2886,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -3004,7 +3004,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>-0.005209523007945031</v>
@@ -3046,7 +3046,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -3252,7 +3252,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>-0.00572709788895107</v>
@@ -3294,7 +3294,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -3412,7 +3412,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>-0.00821656891497979</v>
@@ -3454,7 +3454,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -3572,7 +3572,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>-0.003143760915569587</v>
@@ -3614,7 +3614,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -3820,7 +3820,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>0.0102744813888558</v>
@@ -3862,7 +3862,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -3980,7 +3980,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>0.010155778356459064</v>
@@ -4022,7 +4022,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -4140,7 +4140,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>0.004577178384059716</v>
@@ -4182,7 +4182,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -4388,7 +4388,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>-0.00181633037528572</v>
@@ -4430,7 +4430,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -4548,7 +4548,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>-0.00533539630898254</v>
@@ -4590,7 +4590,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -4708,7 +4708,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>-2.0424717751185207E-4</v>
@@ -4750,7 +4750,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -4956,7 +4956,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>0.004221351128715135</v>
@@ -4998,7 +4998,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -5116,7 +5116,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>0.0024276003051405875</v>
@@ -5158,7 +5158,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -5276,7 +5276,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>-0.002390568292555957</v>
@@ -5318,7 +5318,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -5524,7 +5524,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>0.002376815526289553</v>
@@ -5566,7 +5566,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -5684,7 +5684,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>0.0014018026608490608</v>
@@ -5726,7 +5726,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -5844,7 +5844,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>0.001989965957543396</v>
@@ -5886,7 +5886,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -6092,7 +6092,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>-0.0019131810694534394</v>
@@ -6134,7 +6134,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -6252,7 +6252,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>-0.0038123620445664193</v>
@@ -6294,7 +6294,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -6412,7 +6412,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>0.004508552375268015</v>
@@ -6454,7 +6454,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>

--- a/MR_UKBiobank/ContinuousData/gMR_dat.xlsx
+++ b/MR_UKBiobank/ContinuousData/gMR_dat.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="57">
   <si>
     <t>SNP</t>
   </si>
@@ -88,6 +88,12 @@
   </si>
   <si>
     <t>exposure</t>
+  </si>
+  <si>
+    <t>beta.exposure_corrected</t>
+  </si>
+  <si>
+    <t>se.exposure_corrected</t>
   </si>
   <si>
     <t>action</t>
@@ -311,28 +317,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.038471659868774384</v>
@@ -344,16 +356,16 @@
         <v>0.3860994853562147</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O2" t="n">
         <v>0.005032008685759226</v>
@@ -365,7 +377,7 @@
         <v>214323.0</v>
       </c>
       <c r="R2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -377,42 +389,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.034847248420357774</v>
@@ -424,16 +442,16 @@
         <v>0.2865184791179668</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O3" t="n">
         <v>0.00426676689582343</v>
@@ -445,7 +463,7 @@
         <v>214323.0</v>
       </c>
       <c r="R3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -454,45 +472,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.04849768504033609</v>
@@ -504,16 +528,16 @@
         <v>0.415977286618795</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O4" t="n">
         <v>0.0056440565000923934</v>
@@ -525,7 +549,7 @@
         <v>214323.0</v>
       </c>
       <c r="R4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -537,42 +561,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.07876189247277657</v>
@@ -584,16 +614,16 @@
         <v>0.07108663092621884</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O5" t="n">
         <v>0.006041547412946537</v>
@@ -605,7 +635,7 @@
         <v>214323.0</v>
       </c>
       <c r="R5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -614,45 +644,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.044220478704359564</v>
@@ -664,16 +700,16 @@
         <v>0.25578216057072733</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O6" t="n">
         <v>0.0042214907875013025</v>
@@ -685,7 +721,7 @@
         <v>214323.0</v>
       </c>
       <c r="R6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -697,42 +733,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.07689420144887592</v>
@@ -744,16 +786,16 @@
         <v>0.07819506072610033</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O7" t="n">
         <v>0.005808697524784639</v>
@@ -765,7 +807,7 @@
         <v>214323.0</v>
       </c>
       <c r="R7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -774,21 +816,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -879,28 +927,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.003806498929829664</v>
@@ -912,16 +966,16 @@
         <v>0.38620572013419</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O2" t="n">
         <v>0.004030170706335223</v>
@@ -933,7 +987,7 @@
         <v>351740.0</v>
       </c>
       <c r="R2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -945,42 +999,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>-0.0014198446925235276</v>
@@ -992,16 +1052,16 @@
         <v>0.2858190709046455</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O3" t="n">
         <v>0.0034149447045822763</v>
@@ -1013,7 +1073,7 @@
         <v>351740.0</v>
       </c>
       <c r="R3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -1022,45 +1082,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-3.551722631445365E-4</v>
@@ -1072,16 +1138,16 @@
         <v>0.4160857451526696</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O4" t="n">
         <v>0.004521483480922011</v>
@@ -1093,7 +1159,7 @@
         <v>351740.0</v>
       </c>
       <c r="R4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -1105,42 +1171,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.00785809990604664</v>
@@ -1152,16 +1224,16 @@
         <v>0.07149883436629328</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O5" t="n">
         <v>0.0048267248778757245</v>
@@ -1173,7 +1245,7 @@
         <v>351740.0</v>
       </c>
       <c r="R5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -1182,45 +1254,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.0012062621455166355</v>
@@ -1232,16 +1310,16 @@
         <v>0.2554244612497868</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O6" t="n">
         <v>0.0033802387277976366</v>
@@ -1253,7 +1331,7 @@
         <v>351740.0</v>
       </c>
       <c r="R6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -1265,42 +1343,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.003751338586334582</v>
@@ -1312,16 +1396,16 @@
         <v>0.07842298288508558</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O7" t="n">
         <v>0.0046465029527565085</v>
@@ -1333,7 +1417,7 @@
         <v>351740.0</v>
       </c>
       <c r="R7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -1342,21 +1426,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1447,28 +1537,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.004721641140417785</v>
@@ -1480,16 +1576,16 @@
         <v>0.38613733692172864</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O2" t="n">
         <v>0.004218628330923896</v>
@@ -1501,7 +1597,7 @@
         <v>321778.0</v>
       </c>
       <c r="R2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -1513,42 +1609,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.002636794227644566</v>
@@ -1560,16 +1662,16 @@
         <v>0.2857637874559479</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O3" t="n">
         <v>0.0035752196943523527</v>
@@ -1581,7 +1683,7 @@
         <v>321778.0</v>
       </c>
       <c r="R3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -1590,45 +1692,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.004631981165334541</v>
@@ -1640,16 +1748,16 @@
         <v>0.4160912181690482</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O4" t="n">
         <v>0.004733978556172183</v>
@@ -1661,7 +1769,7 @@
         <v>321778.0</v>
       </c>
       <c r="R4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -1673,42 +1781,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.011016376469789898</v>
@@ -1720,16 +1834,16 @@
         <v>0.07141880426878158</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O5" t="n">
         <v>0.005055918249470786</v>
@@ -1741,7 +1855,7 @@
         <v>321778.0</v>
       </c>
       <c r="R5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -1750,45 +1864,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.004125945725551209</v>
@@ -1800,16 +1920,16 @@
         <v>0.25532820764626546</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O6" t="n">
         <v>0.0035390065561924653</v>
@@ -1821,7 +1941,7 @@
         <v>321778.0</v>
       </c>
       <c r="R6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -1833,42 +1953,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.007260586600120222</v>
@@ -1880,16 +2006,16 @@
         <v>0.0782837857156176</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O7" t="n">
         <v>0.004868445652139601</v>
@@ -1901,7 +2027,7 @@
         <v>321778.0</v>
       </c>
       <c r="R7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -1910,21 +2036,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2015,28 +2147,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.0019172710459829025</v>
@@ -2048,16 +2186,16 @@
         <v>0.3861705061394606</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
         <v>0.003954540639681136</v>
@@ -2069,7 +2207,7 @@
         <v>351741.0</v>
       </c>
       <c r="R2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -2081,42 +2219,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.001735735786979485</v>
@@ -2128,16 +2272,16 @@
         <v>0.285661893268058</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
         <v>0.0033508730577333705</v>
@@ -2149,7 +2293,7 @@
         <v>351741.0</v>
       </c>
       <c r="R3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -2158,45 +2302,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.0031614816960992783</v>
@@ -2208,16 +2358,16 @@
         <v>0.41616132324636596</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O4" t="n">
         <v>0.004438654407112916</v>
@@ -2229,7 +2379,7 @@
         <v>351741.0</v>
       </c>
       <c r="R4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -2241,42 +2391,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>-0.002329592792198533</v>
@@ -2288,16 +2444,16 @@
         <v>0.07142897757156544</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O5" t="n">
         <v>0.004738587670330936</v>
@@ -2309,7 +2465,7 @@
         <v>351741.0</v>
       </c>
       <c r="R5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -2318,45 +2474,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>5.966755594133536E-4</v>
@@ -2368,16 +2530,16 @@
         <v>0.2553981480691759</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O6" t="n">
         <v>0.0033171314234098203</v>
@@ -2389,7 +2551,7 @@
         <v>351741.0</v>
       </c>
       <c r="R6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -2401,42 +2563,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>-0.005226857326711219</v>
@@ -2448,16 +2616,16 @@
         <v>0.07832183339445785</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O7" t="n">
         <v>0.004562198594239567</v>
@@ -2469,7 +2637,7 @@
         <v>351741.0</v>
       </c>
       <c r="R7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -2478,21 +2646,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2583,28 +2757,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.0020197501904204085</v>
@@ -2616,16 +2796,16 @@
         <v>0.3861759093110029</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O2" t="n">
         <v>0.004005742459224765</v>
@@ -2637,7 +2817,7 @@
         <v>351090.0</v>
       </c>
       <c r="R2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -2649,42 +2829,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.002373165821656435</v>
@@ -2696,16 +2882,16 @@
         <v>0.28565040303056194</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O3" t="n">
         <v>0.0033941758725285474</v>
@@ -2717,7 +2903,7 @@
         <v>351090.0</v>
       </c>
       <c r="R3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -2726,45 +2912,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.004101141888513507</v>
@@ -2776,16 +2968,16 @@
         <v>0.41617533965649833</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O4" t="n">
         <v>0.004496342158307523</v>
@@ -2797,7 +2989,7 @@
         <v>351090.0</v>
       </c>
       <c r="R4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -2809,42 +3001,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>-0.0012192712729850042</v>
@@ -2856,16 +3054,16 @@
         <v>0.0714190093708166</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O5" t="n">
         <v>0.004800142531238532</v>
@@ -2877,7 +3075,7 @@
         <v>351090.0</v>
       </c>
       <c r="R5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -2886,45 +3084,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.0037081721462656576</v>
@@ -2936,16 +3140,16 @@
         <v>0.25538750747671535</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O6" t="n">
         <v>0.0033600145803262815</v>
@@ -2957,7 +3161,7 @@
         <v>351090.0</v>
       </c>
       <c r="R6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -2969,42 +3173,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>-0.005209523007945031</v>
@@ -3016,16 +3226,16 @@
         <v>0.07830898060326412</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O7" t="n">
         <v>0.004621506162320852</v>
@@ -3037,7 +3247,7 @@
         <v>351090.0</v>
       </c>
       <c r="R7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -3046,21 +3256,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3151,28 +3367,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>0.013129491545565919</v>
@@ -3184,16 +3406,16 @@
         <v>0.3861251463477502</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O2" t="n">
         <v>0.0038313316283589225</v>
@@ -3205,7 +3427,7 @@
         <v>322007.0</v>
       </c>
       <c r="R2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -3217,42 +3439,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>-0.00572709788895107</v>
@@ -3264,16 +3492,16 @@
         <v>0.28577484340402537</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O3" t="n">
         <v>0.00324718178044719</v>
@@ -3285,7 +3513,7 @@
         <v>322007.0</v>
       </c>
       <c r="R3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -3294,45 +3522,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>0.010396504791458061</v>
@@ -3344,16 +3578,16 @@
         <v>0.416068594782101</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O4" t="n">
         <v>0.004299114963588015</v>
@@ -3365,7 +3599,7 @@
         <v>322007.0</v>
       </c>
       <c r="R4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -3377,42 +3611,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>-0.00821656891497979</v>
@@ -3424,16 +3664,16 @@
         <v>0.07140993829326692</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O5" t="n">
         <v>0.004592260987779454</v>
@@ -3445,7 +3685,7 @@
         <v>322007.0</v>
       </c>
       <c r="R5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -3454,45 +3694,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>-0.015981434408179444</v>
@@ -3504,16 +3750,16 @@
         <v>0.2553391696453804</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O6" t="n">
         <v>0.0032141728119288197</v>
@@ -3525,7 +3771,7 @@
         <v>322007.0</v>
       </c>
       <c r="R6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -3537,42 +3783,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>-0.003143760915569587</v>
@@ -3584,16 +3836,16 @@
         <v>0.07826848484660272</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O7" t="n">
         <v>0.004422106419502881</v>
@@ -3605,7 +3857,7 @@
         <v>322007.0</v>
       </c>
       <c r="R7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -3614,21 +3866,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3719,28 +3977,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.01430583472052661</v>
@@ -3752,16 +4016,16 @@
         <v>0.38617649067297954</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O2" t="n">
         <v>0.003942850180592509</v>
@@ -3773,7 +4037,7 @@
         <v>351452.0</v>
       </c>
       <c r="R2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -3785,42 +4049,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.0102744813888558</v>
@@ -3832,16 +4102,16 @@
         <v>0.28566063075469766</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O3" t="n">
         <v>0.0033409205607358764</v>
@@ -3853,7 +4123,7 @@
         <v>351452.0</v>
       </c>
       <c r="R3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -3862,45 +4132,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.01494086826170413</v>
@@ -3912,16 +4188,16 @@
         <v>0.4161777426220366</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O4" t="n">
         <v>0.004425804551481263</v>
@@ -3933,7 +4209,7 @@
         <v>351452.0</v>
       </c>
       <c r="R4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -3945,42 +4221,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.010155778356459064</v>
@@ -3992,16 +4274,16 @@
         <v>0.07142938438250458</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O5" t="n">
         <v>0.004724536333968606</v>
@@ -4013,7 +4295,7 @@
         <v>351452.0</v>
       </c>
       <c r="R5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -4022,45 +4304,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.014547005081399464</v>
@@ -4072,16 +4360,16 @@
         <v>0.2554118343329957</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O6" t="n">
         <v>0.003307235731756658</v>
@@ -4093,7 +4381,7 @@
         <v>351452.0</v>
       </c>
       <c r="R6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -4105,42 +4393,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.004577178384059716</v>
@@ -4152,16 +4446,16 @@
         <v>0.07833359889828483</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O7" t="n">
         <v>0.004548434774068563</v>
@@ -4173,7 +4467,7 @@
         <v>351452.0</v>
       </c>
       <c r="R7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -4182,21 +4476,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4287,28 +4587,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>0.010998553728101617</v>
@@ -4320,16 +4626,16 @@
         <v>0.3861413501714414</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O2" t="n">
         <v>0.0038981392682733936</v>
@@ -4341,7 +4647,7 @@
         <v>320226.0</v>
       </c>
       <c r="R2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -4353,42 +4659,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>-0.00181633037528572</v>
@@ -4400,16 +4712,16 @@
         <v>0.2857747340940461</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O3" t="n">
         <v>0.0033036372761839176</v>
@@ -4421,7 +4733,7 @@
         <v>320226.0</v>
       </c>
       <c r="R3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -4430,45 +4742,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>0.007021690933490242</v>
@@ -4480,16 +4798,16 @@
         <v>0.41605928313128854</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O4" t="n">
         <v>0.004373662814238708</v>
@@ -4501,7 +4819,7 @@
         <v>320226.0</v>
       </c>
       <c r="R4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -4513,42 +4831,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>-0.00533539630898254</v>
@@ -4560,16 +4884,16 @@
         <v>0.0714276792015639</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O5" t="n">
         <v>0.0046716005000663795</v>
@@ -4581,7 +4905,7 @@
         <v>320226.0</v>
       </c>
       <c r="R5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -4590,45 +4914,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>-0.012450793686876604</v>
@@ -4640,16 +4970,16 @@
         <v>0.2553415400373486</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O6" t="n">
         <v>0.003270096585190361</v>
@@ -4661,7 +4991,7 @@
         <v>320226.0</v>
       </c>
       <c r="R6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -4673,42 +5003,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>-2.0424717751185207E-4</v>
@@ -4720,16 +5056,16 @@
         <v>0.07826972200883127</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O7" t="n">
         <v>0.004498926266961102</v>
@@ -4741,7 +5077,7 @@
         <v>320226.0</v>
       </c>
       <c r="R7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -4750,21 +5086,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4855,28 +5197,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.005889793107628681</v>
@@ -4888,16 +5236,16 @@
         <v>0.3862298201057596</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O2" t="n">
         <v>0.004026882370114043</v>
@@ -4909,7 +5257,7 @@
         <v>350039.0</v>
       </c>
       <c r="R2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -4921,42 +5269,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.004221351128715135</v>
@@ -4968,16 +5322,16 @@
         <v>0.2856553126937284</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O3" t="n">
         <v>0.003411522418330872</v>
@@ -4989,7 +5343,7 @@
         <v>350039.0</v>
       </c>
       <c r="R3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -4998,45 +5352,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.007410104487496083</v>
@@ -5048,16 +5408,16 @@
         <v>0.4162064798493882</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O4" t="n">
         <v>0.00451998730545515</v>
@@ -5069,7 +5429,7 @@
         <v>350039.0</v>
       </c>
       <c r="R4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -5081,42 +5441,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.0024276003051405875</v>
@@ -5128,16 +5494,16 @@
         <v>0.07146203708729598</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O5" t="n">
         <v>0.004823466937374072</v>
@@ -5149,7 +5515,7 @@
         <v>350039.0</v>
       </c>
       <c r="R5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -5158,45 +5524,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.006657255403560866</v>
@@ -5208,16 +5580,16 @@
         <v>0.2554143966815126</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O6" t="n">
         <v>0.003377170083501139</v>
@@ -5229,7 +5601,7 @@
         <v>350039.0</v>
       </c>
       <c r="R6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -5241,42 +5613,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>-0.002390568292555957</v>
@@ -5288,16 +5666,16 @@
         <v>0.07836126831581623</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O7" t="n">
         <v>0.0046438607168498595</v>
@@ -5309,7 +5687,7 @@
         <v>350039.0</v>
       </c>
       <c r="R7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -5318,21 +5696,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5423,28 +5807,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.0038690963135752203</v>
@@ -5456,16 +5846,16 @@
         <v>0.38620414559441557</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O2" t="n">
         <v>0.004023844871261818</v>
@@ -5477,7 +5867,7 @@
         <v>350975.0</v>
       </c>
       <c r="R2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -5489,42 +5879,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.002376815526289553</v>
@@ -5536,16 +5932,16 @@
         <v>0.28563287983474606</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O3" t="n">
         <v>0.0034091825158449026</v>
@@ -5557,7 +5953,7 @@
         <v>350975.0</v>
       </c>
       <c r="R3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -5566,45 +5962,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>0.0017787381903987731</v>
@@ -5616,16 +6018,16 @@
         <v>0.4161720920293468</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O4" t="n">
         <v>0.004516207786443735</v>
@@ -5637,7 +6039,7 @@
         <v>350975.0</v>
       </c>
       <c r="R4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -5649,42 +6051,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.0014018026608490608</v>
@@ -5696,16 +6104,16 @@
         <v>0.07144098582520123</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O5" t="n">
         <v>0.004820797855989508</v>
@@ -5717,7 +6125,7 @@
         <v>350975.0</v>
       </c>
       <c r="R5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -5726,45 +6134,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>5.780395479382013E-4</v>
@@ -5776,16 +6190,16 @@
         <v>0.2553714652040744</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O6" t="n">
         <v>0.0033749057604561977</v>
@@ -5797,7 +6211,7 @@
         <v>350975.0</v>
       </c>
       <c r="R6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -5809,42 +6223,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.001989965957543396</v>
@@ -5856,16 +6276,16 @@
         <v>0.0783275162048579</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O7" t="n">
         <v>0.004641547433226485</v>
@@ -5877,7 +6297,7 @@
         <v>350975.0</v>
       </c>
       <c r="R7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -5886,21 +6306,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5991,28 +6417,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>9.376095324920829E-4</v>
@@ -6024,16 +6456,16 @@
         <v>0.3863922286237116</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O2" t="n">
         <v>0.004513283631340966</v>
@@ -6045,7 +6477,7 @@
         <v>279796.0</v>
       </c>
       <c r="R2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -6057,42 +6489,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>-0.0019131810694534394</v>
@@ -6104,16 +6542,16 @@
         <v>0.28564203919998854</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O3" t="n">
         <v>0.0038215938171244743</v>
@@ -6125,7 +6563,7 @@
         <v>279796.0</v>
       </c>
       <c r="R3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -6134,45 +6572,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>3.616398040624297E-5</v>
@@ -6184,16 +6628,16 @@
         <v>0.4160906517605684</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O4" t="n">
         <v>0.005060575174380083</v>
@@ -6205,7 +6649,7 @@
         <v>279796.0</v>
       </c>
       <c r="R4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -6217,42 +6661,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>-0.0038123620445664193</v>
@@ -6264,16 +6714,16 @@
         <v>0.07131803170881643</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O5" t="n">
         <v>0.005407966097689434</v>
@@ -6285,7 +6735,7 @@
         <v>279796.0</v>
       </c>
       <c r="R5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -6294,45 +6744,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>-5.458104459678437E-4</v>
@@ -6344,16 +6800,16 @@
         <v>0.25526812391885517</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O6" t="n">
         <v>0.0037831049092283955</v>
@@ -6365,7 +6821,7 @@
         <v>279796.0</v>
       </c>
       <c r="R6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -6377,42 +6833,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.004508552375268015</v>
@@ -6424,16 +6886,16 @@
         <v>0.07824450671203305</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O7" t="n">
         <v>0.005205342617545942</v>
@@ -6445,7 +6907,7 @@
         <v>279796.0</v>
       </c>
       <c r="R7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -6454,21 +6916,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>

--- a/MR_UKBiobank/ContinuousData/gMR_dat.xlsx
+++ b/MR_UKBiobank/ContinuousData/gMR_dat.xlsx
@@ -69,10 +69,16 @@
     <t>p.outcome</t>
   </si>
   <si>
-    <t>n.outcome</t>
+    <t>outcome</t>
   </si>
   <si>
-    <t>outcome</t>
+    <t>mean.outcome</t>
+  </si>
+  <si>
+    <t>std.outcome</t>
+  </si>
+  <si>
+    <t>n.outcome</t>
   </si>
   <si>
     <t>pval.exposure</t>
@@ -88,12 +94,6 @@
   </si>
   <si>
     <t>exposure</t>
-  </si>
-  <si>
-    <t>beta.exposure_corrected</t>
-  </si>
-  <si>
-    <t>se.exposure_corrected</t>
   </si>
   <si>
     <t>action</t>
@@ -347,13 +347,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.038471659868774384</v>
+        <v>-0.03860754964140986</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3860994853562147</v>
+        <v>0.5424131865268096</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -368,37 +368,37 @@
         <v>44</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005032008685759226</v>
+        <v>0.006288049695777749</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0917594908219566E-14</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>214323.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>8.283427175683998E-10</v>
+      </c>
+      <c r="Q2" t="s">
         <v>44</v>
       </c>
+      <c r="R2" t="n">
+        <v>0.5406392019747939</v>
+      </c>
       <c r="S2" t="n">
+        <v>0.1363329839542408</v>
+      </c>
+      <c r="T2" t="n">
+        <v>138141.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -433,13 +433,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.034847248420357774</v>
+        <v>0.02962742820380026</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2865184791179668</v>
+        <v>0.34768823158946294</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -454,37 +454,37 @@
         <v>44</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00426676689582343</v>
+        <v>0.005322829137507404</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1749936875029794E-16</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>214323.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>2.6097742182363325E-8</v>
+      </c>
+      <c r="Q3" t="s">
         <v>44</v>
       </c>
+      <c r="R3" t="n">
+        <v>0.5406392019747939</v>
+      </c>
       <c r="S3" t="n">
+        <v>0.1363329839542408</v>
+      </c>
+      <c r="T3" t="n">
+        <v>138141.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -519,13 +519,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04849768504033609</v>
+        <v>-0.04682543749102529</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.415977286618795</v>
+        <v>0.6011864688977204</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -540,37 +540,37 @@
         <v>44</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0056440565000923934</v>
+        <v>0.007046052315045322</v>
       </c>
       <c r="P4" t="n">
-        <v>8.550548359273012E-18</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>214323.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>3.030439163737735E-11</v>
+      </c>
+      <c r="Q4" t="s">
         <v>44</v>
       </c>
+      <c r="R4" t="n">
+        <v>0.5406392019747939</v>
+      </c>
       <c r="S4" t="n">
+        <v>0.1363329839542408</v>
+      </c>
+      <c r="T4" t="n">
+        <v>138141.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -605,13 +605,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07876189247277657</v>
+        <v>0.06973788810920274</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07108663092621884</v>
+        <v>0.07349374914037107</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -626,37 +626,37 @@
         <v>44</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006041547412946537</v>
+        <v>0.007560665451432363</v>
       </c>
       <c r="P5" t="n">
-        <v>7.827529907766851E-39</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>214323.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>2.906862219845919E-20</v>
+      </c>
+      <c r="Q5" t="s">
         <v>44</v>
       </c>
+      <c r="R5" t="n">
+        <v>0.5406392019747939</v>
+      </c>
       <c r="S5" t="n">
+        <v>0.1363329839542408</v>
+      </c>
+      <c r="T5" t="n">
+        <v>138141.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -691,13 +691,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.044220478704359564</v>
+        <v>0.0388191978491372</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25578216057072733</v>
+        <v>0.3025676663698685</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -712,37 +712,37 @@
         <v>44</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0042214907875013025</v>
+        <v>0.005268241167356963</v>
       </c>
       <c r="P6" t="n">
-        <v>1.140542963564186E-25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>214323.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>1.7347506046090062E-13</v>
+      </c>
+      <c r="Q6" t="s">
         <v>44</v>
       </c>
+      <c r="R6" t="n">
+        <v>0.5406392019747939</v>
+      </c>
       <c r="S6" t="n">
+        <v>0.1363329839542408</v>
+      </c>
+      <c r="T6" t="n">
+        <v>138141.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -777,13 +777,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07689420144887592</v>
+        <v>0.06743350790603107</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07819506072610033</v>
+        <v>0.08112001505707936</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -798,37 +798,37 @@
         <v>44</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005808697524784639</v>
+        <v>0.0072664521680964435</v>
       </c>
       <c r="P7" t="n">
-        <v>5.506037300184767E-40</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>214323.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>1.7163672952522476E-20</v>
+      </c>
+      <c r="Q7" t="s">
         <v>44</v>
       </c>
+      <c r="R7" t="n">
+        <v>0.5406392019747939</v>
+      </c>
       <c r="S7" t="n">
+        <v>0.1363329839542408</v>
+      </c>
+      <c r="T7" t="n">
+        <v>138141.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -957,13 +957,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.003806498929829664</v>
+        <v>-0.0025938780512247237</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38620572013419</v>
+        <v>0.5424724459195728</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -978,37 +978,37 @@
         <v>55</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004030170706335223</v>
+        <v>0.004954205701469752</v>
       </c>
       <c r="P2" t="n">
-        <v>0.34491450873823615</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>351740.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.6005775120437286</v>
+      </c>
+      <c r="Q2" t="s">
         <v>55</v>
       </c>
+      <c r="R2" t="n">
+        <v>36.07437243337041</v>
+      </c>
       <c r="S2" t="n">
+        <v>6.583796061060719</v>
+      </c>
+      <c r="T2" t="n">
+        <v>231091.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -1043,13 +1043,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0014198446925235276</v>
+        <v>-0.0056970242207360485</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2858190709046455</v>
+        <v>0.34723983192768215</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -1064,37 +1064,37 @@
         <v>55</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0034149447045822763</v>
+        <v>0.004197085282006314</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6775757525992285</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>351740.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.17466299059001633</v>
+      </c>
+      <c r="Q3" t="s">
         <v>55</v>
       </c>
+      <c r="R3" t="n">
+        <v>36.07437243337041</v>
+      </c>
       <c r="S3" t="n">
+        <v>6.583796061060719</v>
+      </c>
+      <c r="T3" t="n">
+        <v>231091.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -1129,13 +1129,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.551722631445365E-4</v>
+        <v>-0.003660777914400295</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4160857451526696</v>
+        <v>0.60199228875205</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -1150,37 +1150,37 @@
         <v>55</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004521483480922011</v>
+        <v>0.005566912652613397</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9373888907659219</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>351740.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.5107986027817576</v>
+      </c>
+      <c r="Q4" t="s">
         <v>55</v>
       </c>
+      <c r="R4" t="n">
+        <v>36.07437243337041</v>
+      </c>
       <c r="S4" t="n">
+        <v>6.583796061060719</v>
+      </c>
+      <c r="T4" t="n">
+        <v>231091.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -1215,13 +1215,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00785809990604664</v>
+        <v>2.947822253150711E-4</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07149883436629328</v>
+        <v>0.07373285848432003</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -1236,37 +1236,37 @@
         <v>55</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0048267248778757245</v>
+        <v>0.005951857318913005</v>
       </c>
       <c r="P5" t="n">
-        <v>0.10351735565852002</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>351740.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.9604987492338425</v>
+      </c>
+      <c r="Q5" t="s">
         <v>55</v>
       </c>
+      <c r="R5" t="n">
+        <v>36.07437243337041</v>
+      </c>
       <c r="S5" t="n">
+        <v>6.583796061060719</v>
+      </c>
+      <c r="T5" t="n">
+        <v>231091.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -1301,13 +1301,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0012062621455166355</v>
+        <v>-0.004978791574197257</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2554244612497868</v>
+        <v>0.30229433426658764</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -1322,37 +1322,37 @@
         <v>55</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0033802387277976366</v>
+        <v>0.0041553252409936205</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7211990109745776</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>351740.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.23085155282066228</v>
+      </c>
+      <c r="Q6" t="s">
         <v>55</v>
       </c>
+      <c r="R6" t="n">
+        <v>36.07437243337041</v>
+      </c>
       <c r="S6" t="n">
+        <v>6.583796061060719</v>
+      </c>
+      <c r="T6" t="n">
+        <v>231091.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -1387,13 +1387,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003751338586334582</v>
+        <v>-3.008403681995109E-4</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07842298288508558</v>
+        <v>0.08110224976308035</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -1408,37 +1408,37 @@
         <v>55</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0046465029527565085</v>
+        <v>0.005729227257350238</v>
       </c>
       <c r="P7" t="n">
-        <v>0.41946734120033724</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>351740.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.9581225613275717</v>
+      </c>
+      <c r="Q7" t="s">
         <v>55</v>
       </c>
+      <c r="R7" t="n">
+        <v>36.07437243337041</v>
+      </c>
       <c r="S7" t="n">
+        <v>6.583796061060719</v>
+      </c>
+      <c r="T7" t="n">
+        <v>231091.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -1567,13 +1567,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.004721641140417785</v>
+        <v>-0.008157150454670654</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38613733692172864</v>
+        <v>0.5421098410717493</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -1588,37 +1588,37 @@
         <v>56</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004218628330923896</v>
+        <v>0.005176591486131346</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2630402618716589</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>321778.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.11507884929731606</v>
+      </c>
+      <c r="Q2" t="s">
         <v>56</v>
       </c>
+      <c r="R2" t="n">
+        <v>5.130382132153426</v>
+      </c>
       <c r="S2" t="n">
+        <v>1.2376540722195797</v>
+      </c>
+      <c r="T2" t="n">
+        <v>211542.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -1653,13 +1653,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002636794227644566</v>
+        <v>9.320714163573189E-5</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2857637874559479</v>
+        <v>0.3473423717276002</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -1674,37 +1674,37 @@
         <v>56</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0035752196943523527</v>
+        <v>0.004388129652186869</v>
       </c>
       <c r="P3" t="n">
-        <v>0.46080702938192275</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>321778.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.9830536320725021</v>
+      </c>
+      <c r="Q3" t="s">
         <v>56</v>
       </c>
+      <c r="R3" t="n">
+        <v>5.130382132153426</v>
+      </c>
       <c r="S3" t="n">
+        <v>1.2376540722195797</v>
+      </c>
+      <c r="T3" t="n">
+        <v>211542.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -1739,13 +1739,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.004631981165334541</v>
+        <v>-0.011400852534722661</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4160912181690482</v>
+        <v>0.6018473872800674</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -1760,37 +1760,37 @@
         <v>56</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004733978556172183</v>
+        <v>0.005815807564149078</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3278504721819454</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>321778.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.04995953668654066</v>
+      </c>
+      <c r="Q4" t="s">
         <v>56</v>
       </c>
+      <c r="R4" t="n">
+        <v>5.130382132153426</v>
+      </c>
       <c r="S4" t="n">
+        <v>1.2376540722195797</v>
+      </c>
+      <c r="T4" t="n">
+        <v>211542.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -1825,13 +1825,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.011016376469789898</v>
+        <v>0.008789944993407028</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07141880426878158</v>
+        <v>0.0738009473296083</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -1846,37 +1846,37 @@
         <v>56</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005055918249470786</v>
+        <v>0.006221829851609203</v>
       </c>
       <c r="P5" t="n">
-        <v>0.029339288827796225</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>321778.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.15772812175652712</v>
+      </c>
+      <c r="Q5" t="s">
         <v>56</v>
       </c>
+      <c r="R5" t="n">
+        <v>5.130382132153426</v>
+      </c>
       <c r="S5" t="n">
+        <v>1.2376540722195797</v>
+      </c>
+      <c r="T5" t="n">
+        <v>211542.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -1911,13 +1911,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004125945725551209</v>
+        <v>-3.853063552155892E-4</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25532820764626546</v>
+        <v>0.3023702148982235</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -1932,37 +1932,37 @@
         <v>56</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0035390065561924653</v>
+        <v>0.004344802972273344</v>
       </c>
       <c r="P6" t="n">
-        <v>0.24367654078858822</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>321778.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.9293346236213091</v>
+      </c>
+      <c r="Q6" t="s">
         <v>56</v>
       </c>
+      <c r="R6" t="n">
+        <v>5.130382132153426</v>
+      </c>
       <c r="S6" t="n">
+        <v>1.2376540722195797</v>
+      </c>
+      <c r="T6" t="n">
+        <v>211542.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -1997,13 +1997,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007260586600120222</v>
+        <v>0.007032619976154515</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0782837857156176</v>
+        <v>0.08112809749364193</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -2018,37 +2018,37 @@
         <v>56</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004868445652139601</v>
+        <v>0.005989976951437902</v>
       </c>
       <c r="P7" t="n">
-        <v>0.13586898185601698</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>321778.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.24037046769076487</v>
+      </c>
+      <c r="Q7" t="s">
         <v>56</v>
       </c>
+      <c r="R7" t="n">
+        <v>5.130382132153426</v>
+      </c>
       <c r="S7" t="n">
+        <v>1.2376540722195797</v>
+      </c>
+      <c r="T7" t="n">
+        <v>211542.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -2177,13 +2177,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0019172710459829025</v>
+        <v>-5.105838063863884E-4</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3861705061394606</v>
+        <v>0.5423421709254607</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -2198,37 +2198,37 @@
         <v>47</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003954540639681136</v>
+        <v>0.004875141629581205</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6277988374115242</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>351741.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.916588483069708</v>
+      </c>
+      <c r="Q2" t="s">
         <v>47</v>
       </c>
+      <c r="R2" t="n">
+        <v>5.700182583990279</v>
+      </c>
       <c r="S2" t="n">
+        <v>1.1490326037283973</v>
+      </c>
+      <c r="T2" t="n">
+        <v>231247.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -2263,13 +2263,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001735735786979485</v>
+        <v>0.001063489809179161</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.285661893268058</v>
+        <v>0.3471504495193451</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -2284,37 +2284,37 @@
         <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0033508730577333705</v>
+        <v>0.004130578164521665</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6044620217560218</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>351741.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.7968180973382162</v>
+      </c>
+      <c r="Q3" t="s">
         <v>47</v>
       </c>
+      <c r="R3" t="n">
+        <v>5.700182583990279</v>
+      </c>
       <c r="S3" t="n">
+        <v>1.1490326037283973</v>
+      </c>
+      <c r="T3" t="n">
+        <v>231247.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -2349,13 +2349,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0031614816960992783</v>
+        <v>-0.005563097021752728</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41616132324636596</v>
+        <v>0.6018997003204366</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -2370,37 +2370,37 @@
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004438654407112916</v>
+        <v>0.005477396730130087</v>
       </c>
       <c r="P4" t="n">
-        <v>0.47630346494143017</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>351741.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.3097989720398852</v>
+      </c>
+      <c r="Q4" t="s">
         <v>47</v>
       </c>
+      <c r="R4" t="n">
+        <v>5.700182583990279</v>
+      </c>
       <c r="S4" t="n">
+        <v>1.1490326037283973</v>
+      </c>
+      <c r="T4" t="n">
+        <v>231247.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -2435,13 +2435,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.002329592792198533</v>
+        <v>0.00201776330876144</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07142897757156544</v>
+        <v>0.07372203747508076</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -2456,37 +2456,37 @@
         <v>47</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004738587670330936</v>
+        <v>0.005857652096239367</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6229870671951037</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>351741.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.7304960048941784</v>
+      </c>
+      <c r="Q5" t="s">
         <v>47</v>
       </c>
+      <c r="R5" t="n">
+        <v>5.700182583990279</v>
+      </c>
       <c r="S5" t="n">
+        <v>1.1490326037283973</v>
+      </c>
+      <c r="T5" t="n">
+        <v>231247.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -2521,13 +2521,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>5.966755594133536E-4</v>
+        <v>0.0010466365082535272</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2553981480691759</v>
+        <v>0.3023325708009185</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -2542,37 +2542,37 @@
         <v>47</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0033171314234098203</v>
+        <v>0.0040898436926803255</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8572492568481525</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>351741.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.7980196902684511</v>
+      </c>
+      <c r="Q6" t="s">
         <v>47</v>
       </c>
+      <c r="R6" t="n">
+        <v>5.700182583990279</v>
+      </c>
       <c r="S6" t="n">
+        <v>1.1490326037283973</v>
+      </c>
+      <c r="T6" t="n">
+        <v>231247.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -2607,13 +2607,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.005226857326711219</v>
+        <v>-3.0998116441170986E-4</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07832183339445785</v>
+        <v>0.08108645733782492</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -2628,37 +2628,37 @@
         <v>47</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004562198594239567</v>
+        <v>0.0056384406869021885</v>
       </c>
       <c r="P7" t="n">
-        <v>0.25192494655024866</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>351741.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.9561573137908761</v>
+      </c>
+      <c r="Q7" t="s">
         <v>47</v>
       </c>
+      <c r="R7" t="n">
+        <v>5.700182583990279</v>
+      </c>
       <c r="S7" t="n">
+        <v>1.1490326037283973</v>
+      </c>
+      <c r="T7" t="n">
+        <v>231247.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -2787,13 +2787,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0020197501904204085</v>
+        <v>-0.00154522682325348</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3861759093110029</v>
+        <v>0.542365831784447</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -2808,37 +2808,37 @@
         <v>48</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004005742459224765</v>
+        <v>0.004939705340019955</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6141115369651446</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>351090.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.754419517440928</v>
+      </c>
+      <c r="Q2" t="s">
         <v>48</v>
       </c>
+      <c r="R2" t="n">
+        <v>3.5598532132350713</v>
+      </c>
       <c r="S2" t="n">
+        <v>0.8729815505568264</v>
+      </c>
+      <c r="T2" t="n">
+        <v>230811.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -2873,13 +2873,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002373165821656435</v>
+        <v>0.002810415002508393</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28565040303056194</v>
+        <v>0.3470978419572724</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -2894,37 +2894,37 @@
         <v>48</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0033941758725285474</v>
+        <v>0.004185244061678828</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4844352364139075</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>351090.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.5018991382526535</v>
+      </c>
+      <c r="Q3" t="s">
         <v>48</v>
       </c>
+      <c r="R3" t="n">
+        <v>3.5598532132350713</v>
+      </c>
       <c r="S3" t="n">
+        <v>0.8729815505568264</v>
+      </c>
+      <c r="T3" t="n">
+        <v>230811.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -2959,13 +2959,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.004101141888513507</v>
+        <v>-0.006524545535169864</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41617533965649833</v>
+        <v>0.6019275511132485</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -2980,37 +2980,37 @@
         <v>48</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004496342158307523</v>
+        <v>0.00555014762802485</v>
       </c>
       <c r="P4" t="n">
-        <v>0.36171340270922425</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>351090.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.23977095254547723</v>
+      </c>
+      <c r="Q4" t="s">
         <v>48</v>
       </c>
+      <c r="R4" t="n">
+        <v>3.5598532132350713</v>
+      </c>
       <c r="S4" t="n">
+        <v>0.8729815505568264</v>
+      </c>
+      <c r="T4" t="n">
+        <v>230811.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -3045,13 +3045,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0012192712729850042</v>
+        <v>0.0034808306407061694</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0714190093708166</v>
+        <v>0.07369449462980533</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -3066,37 +3066,37 @@
         <v>48</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004800142531238532</v>
+        <v>0.005935963658891267</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7994900625223643</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>351090.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.5576094058927762</v>
+      </c>
+      <c r="Q5" t="s">
         <v>48</v>
       </c>
+      <c r="R5" t="n">
+        <v>3.5598532132350713</v>
+      </c>
       <c r="S5" t="n">
+        <v>0.8729815505568264</v>
+      </c>
+      <c r="T5" t="n">
+        <v>230811.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -3131,13 +3131,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0037081721462656576</v>
+        <v>0.004175785859465325</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25538750747671535</v>
+        <v>0.3022667897110623</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -3152,37 +3152,37 @@
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0033600145803262815</v>
+        <v>0.0041440274229981545</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2697596909558039</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>351090.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.31361701052574054</v>
+      </c>
+      <c r="Q6" t="s">
         <v>48</v>
       </c>
+      <c r="R6" t="n">
+        <v>3.5598532132350713</v>
+      </c>
       <c r="S6" t="n">
+        <v>0.8729815505568264</v>
+      </c>
+      <c r="T6" t="n">
+        <v>230811.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -3217,13 +3217,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.005209523007945031</v>
+        <v>-3.8466424010985783E-4</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07830898060326412</v>
+        <v>0.08105766189653006</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -3238,37 +3238,37 @@
         <v>48</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004621506162320852</v>
+        <v>0.005713818270384449</v>
       </c>
       <c r="P7" t="n">
-        <v>0.25964395143949504</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>351090.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.9463256211868963</v>
+      </c>
+      <c r="Q7" t="s">
         <v>48</v>
       </c>
+      <c r="R7" t="n">
+        <v>3.5598532132350713</v>
+      </c>
       <c r="S7" t="n">
+        <v>0.8729815505568264</v>
+      </c>
+      <c r="T7" t="n">
+        <v>230811.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -3397,13 +3397,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.013129491545565919</v>
+        <v>0.013227206965669432</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3861251463477502</v>
+        <v>0.5421626984126984</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -3418,37 +3418,37 @@
         <v>49</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0038313316283589225</v>
+        <v>0.0047297576375006185</v>
       </c>
       <c r="P2" t="n">
-        <v>6.106480778575935E-4</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>322007.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.0051649206611189356</v>
+      </c>
+      <c r="Q2" t="s">
         <v>49</v>
       </c>
+      <c r="R2" t="n">
+        <v>1.4491140447845805</v>
+      </c>
       <c r="S2" t="n">
+        <v>0.38289400307526095</v>
+      </c>
+      <c r="T2" t="n">
+        <v>211680.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -3483,13 +3483,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.00572709788895107</v>
+        <v>-0.0061987840672830625</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28577484340402537</v>
+        <v>0.34730961829176116</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -3504,37 +3504,37 @@
         <v>49</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00324718178044719</v>
+        <v>0.0040091796899764335</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07778119882869097</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>322007.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.12207038938486411</v>
+      </c>
+      <c r="Q3" t="s">
         <v>49</v>
       </c>
+      <c r="R3" t="n">
+        <v>1.4491140447845805</v>
+      </c>
       <c r="S3" t="n">
+        <v>0.38289400307526095</v>
+      </c>
+      <c r="T3" t="n">
+        <v>211680.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -3569,13 +3569,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.010396504791458061</v>
+        <v>0.007380849848315527</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.416068594782101</v>
+        <v>0.6018683862433862</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -3590,37 +3590,37 @@
         <v>49</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004299114963588015</v>
+        <v>0.005313876336351969</v>
       </c>
       <c r="P4" t="n">
-        <v>0.015594213886514784</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>322007.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.16484132923230987</v>
+      </c>
+      <c r="Q4" t="s">
         <v>49</v>
       </c>
+      <c r="R4" t="n">
+        <v>1.4491140447845805</v>
+      </c>
       <c r="S4" t="n">
+        <v>0.38289400307526095</v>
+      </c>
+      <c r="T4" t="n">
+        <v>211680.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -3655,13 +3655,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.00821656891497979</v>
+        <v>-0.0076213878965980895</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07140993829326692</v>
+        <v>0.07377173091458805</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -3676,37 +3676,37 @@
         <v>49</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004592260987779454</v>
+        <v>0.005685387248796478</v>
       </c>
       <c r="P5" t="n">
-        <v>0.07358020142279681</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>322007.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.18007706632403073</v>
+      </c>
+      <c r="Q5" t="s">
         <v>49</v>
       </c>
+      <c r="R5" t="n">
+        <v>1.4491140447845805</v>
+      </c>
       <c r="S5" t="n">
+        <v>0.38289400307526095</v>
+      </c>
+      <c r="T5" t="n">
+        <v>211680.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -3741,13 +3741,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.015981434408179444</v>
+        <v>-0.01418804756452663</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2553391696453804</v>
+        <v>0.30235496976568405</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -3762,37 +3762,37 @@
         <v>49</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0032141728119288197</v>
+        <v>0.003969549704543838</v>
       </c>
       <c r="P6" t="n">
-        <v>6.623932728278276E-7</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>322007.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>3.513503320250137E-4</v>
+      </c>
+      <c r="Q6" t="s">
         <v>49</v>
       </c>
+      <c r="R6" t="n">
+        <v>1.4491140447845805</v>
+      </c>
       <c r="S6" t="n">
+        <v>0.38289400307526095</v>
+      </c>
+      <c r="T6" t="n">
+        <v>211680.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -3827,13 +3827,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.003143760915569587</v>
+        <v>-0.0018230709845848102</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07826848484660272</v>
+        <v>0.081098828420257</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -3848,37 +3848,37 @@
         <v>49</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004422106419502881</v>
+        <v>0.00547351838541868</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4771347442107754</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>322007.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.7390809169177737</v>
+      </c>
+      <c r="Q7" t="s">
         <v>49</v>
       </c>
+      <c r="R7" t="n">
+        <v>1.4491140447845805</v>
+      </c>
       <c r="S7" t="n">
+        <v>0.38289400307526095</v>
+      </c>
+      <c r="T7" t="n">
+        <v>211680.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -4007,13 +4007,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.01430583472052661</v>
+        <v>-0.01679056771544822</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38617649067297954</v>
+        <v>0.5423618775563201</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -4028,37 +4028,37 @@
         <v>50</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003942850180592509</v>
+        <v>0.00486011075067976</v>
       </c>
       <c r="P2" t="n">
-        <v>2.853364346669936E-4</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>351452.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>5.508600103366399E-4</v>
+      </c>
+      <c r="Q2" t="s">
         <v>50</v>
       </c>
+      <c r="R2" t="n">
+        <v>1.7633706550671948</v>
+      </c>
       <c r="S2" t="n">
+        <v>1.0219125546496655</v>
+      </c>
+      <c r="T2" t="n">
+        <v>231045.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -4093,13 +4093,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0102744813888558</v>
+        <v>0.009406560034825966</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28566063075469766</v>
+        <v>0.34714882382219914</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -4114,37 +4114,37 @@
         <v>50</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0033409205607358764</v>
+        <v>0.004117828126072445</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0021027572696300178</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>351452.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.022351881406601586</v>
+      </c>
+      <c r="Q3" t="s">
         <v>50</v>
       </c>
+      <c r="R3" t="n">
+        <v>1.7633706550671948</v>
+      </c>
       <c r="S3" t="n">
+        <v>1.0219125546496655</v>
+      </c>
+      <c r="T3" t="n">
+        <v>231045.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -4179,13 +4179,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.01494086826170413</v>
+        <v>-0.01547700240491007</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161777426220366</v>
+        <v>0.6019087190806985</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -4200,37 +4200,37 @@
         <v>50</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004425804551481263</v>
+        <v>0.005460710958549628</v>
       </c>
       <c r="P4" t="n">
-        <v>7.359502464391945E-4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>351452.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.004593782876831189</v>
+      </c>
+      <c r="Q4" t="s">
         <v>50</v>
       </c>
+      <c r="R4" t="n">
+        <v>1.7633706550671948</v>
+      </c>
       <c r="S4" t="n">
+        <v>1.0219125546496655</v>
+      </c>
+      <c r="T4" t="n">
+        <v>231045.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -4265,13 +4265,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.010155778356459064</v>
+        <v>0.016795549985328225</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07142938438250458</v>
+        <v>0.07371074898829233</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -4286,37 +4286,37 @@
         <v>50</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004724536333968606</v>
+        <v>0.005839656906415905</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03158897235278783</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>351452.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.004026343141968958</v>
+      </c>
+      <c r="Q5" t="s">
         <v>50</v>
       </c>
+      <c r="R5" t="n">
+        <v>1.7633706550671948</v>
+      </c>
       <c r="S5" t="n">
+        <v>1.0219125546496655</v>
+      </c>
+      <c r="T5" t="n">
+        <v>231045.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -4351,13 +4351,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.014547005081399464</v>
+        <v>0.016042542588321662</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2554118343329957</v>
+        <v>0.30233287887640936</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -4372,37 +4372,37 @@
         <v>50</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003307235731756658</v>
+        <v>0.0040771005401681205</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0901405269863E-5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>351452.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>8.329311091824982E-5</v>
+      </c>
+      <c r="Q6" t="s">
         <v>50</v>
       </c>
+      <c r="R6" t="n">
+        <v>1.7633706550671948</v>
+      </c>
       <c r="S6" t="n">
+        <v>1.0219125546496655</v>
+      </c>
+      <c r="T6" t="n">
+        <v>231045.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -4437,13 +4437,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004577178384059716</v>
+        <v>0.009970939037620594</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07833359889828483</v>
+        <v>0.08107944339847216</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -4458,37 +4458,37 @@
         <v>50</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004548434774068563</v>
+        <v>0.0056209859950781494</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3142626196608318</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>351452.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.07608477761304709</v>
+      </c>
+      <c r="Q7" t="s">
         <v>50</v>
       </c>
+      <c r="R7" t="n">
+        <v>1.7633706550671948</v>
+      </c>
       <c r="S7" t="n">
+        <v>1.0219125546496655</v>
+      </c>
+      <c r="T7" t="n">
+        <v>231045.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -4617,13 +4617,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.010998553728101617</v>
+        <v>0.011751615139896702</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3861413501714414</v>
+        <v>0.5422497743575128</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -4638,37 +4638,37 @@
         <v>51</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0038981392682733936</v>
+        <v>0.004814737348237028</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004780434618875145</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>320226.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.014657236783354005</v>
+      </c>
+      <c r="Q2" t="s">
         <v>51</v>
       </c>
+      <c r="R2" t="n">
+        <v>1.540748824283882</v>
+      </c>
       <c r="S2" t="n">
+        <v>0.2708679489221865</v>
+      </c>
+      <c r="T2" t="n">
+        <v>210510.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -4703,13 +4703,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.00181633037528572</v>
+        <v>-0.004167570499224751</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2857747340940461</v>
+        <v>0.34723528573464446</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -4724,37 +4724,37 @@
         <v>51</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0033036372761839176</v>
+        <v>0.00408048352770448</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5824588937437769</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>320226.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.30709345800108756</v>
+      </c>
+      <c r="Q3" t="s">
         <v>51</v>
       </c>
+      <c r="R3" t="n">
+        <v>1.540748824283882</v>
+      </c>
       <c r="S3" t="n">
+        <v>0.2708679489221865</v>
+      </c>
+      <c r="T3" t="n">
+        <v>210510.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -4789,13 +4789,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007021690933490242</v>
+        <v>0.0028513059472051877</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41605928313128854</v>
+        <v>0.6019452757588714</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -4810,37 +4810,37 @@
         <v>51</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004373662814238708</v>
+        <v>0.005408874313332539</v>
       </c>
       <c r="P4" t="n">
-        <v>0.10839609774250065</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>320226.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.5980876908786741</v>
+      </c>
+      <c r="Q4" t="s">
         <v>51</v>
       </c>
+      <c r="R4" t="n">
+        <v>1.540748824283882</v>
+      </c>
       <c r="S4" t="n">
+        <v>0.2708679489221865</v>
+      </c>
+      <c r="T4" t="n">
+        <v>210510.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -4875,13 +4875,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.00533539630898254</v>
+        <v>-0.006267557271987062</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0714276792015639</v>
+        <v>0.07377559260842716</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -4896,37 +4896,37 @@
         <v>51</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0046716005000663795</v>
+        <v>0.005786832309573213</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2534167455661521</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>320226.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.27877761240836835</v>
+      </c>
+      <c r="Q5" t="s">
         <v>51</v>
       </c>
+      <c r="R5" t="n">
+        <v>1.540748824283882</v>
+      </c>
       <c r="S5" t="n">
+        <v>0.2708679489221865</v>
+      </c>
+      <c r="T5" t="n">
+        <v>210510.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -4961,13 +4961,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.012450793686876604</v>
+        <v>-0.013357086392654474</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2553415400373486</v>
+        <v>0.3022873022659256</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -4982,37 +4982,37 @@
         <v>51</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003270096585190361</v>
+        <v>0.00404022159977643</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4042207644442674E-4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>320226.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>9.464439640220786E-4</v>
+      </c>
+      <c r="Q6" t="s">
         <v>51</v>
       </c>
+      <c r="R6" t="n">
+        <v>1.540748824283882</v>
+      </c>
       <c r="S6" t="n">
+        <v>0.2708679489221865</v>
+      </c>
+      <c r="T6" t="n">
+        <v>210510.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -5047,13 +5047,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0424717751185207E-4</v>
+        <v>-9.942294441442334E-4</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07826972200883127</v>
+        <v>0.08106740772409862</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -5068,37 +5068,37 @@
         <v>51</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004498926266961102</v>
+        <v>0.0055719847023537935</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9637892312570266</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>320226.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.8583826136358336</v>
+      </c>
+      <c r="Q7" t="s">
         <v>51</v>
       </c>
+      <c r="R7" t="n">
+        <v>1.540748824283882</v>
+      </c>
       <c r="S7" t="n">
+        <v>0.2708679489221865</v>
+      </c>
+      <c r="T7" t="n">
+        <v>210510.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -5227,13 +5227,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.005889793107628681</v>
+        <v>-0.005433166101887944</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3862298201057596</v>
+        <v>0.5424709921341967</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -5248,37 +5248,37 @@
         <v>52</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004026882370114043</v>
+        <v>0.004969604374995328</v>
       </c>
       <c r="P2" t="n">
-        <v>0.14357266506237049</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>350039.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.27427228815491006</v>
+      </c>
+      <c r="Q2" t="s">
         <v>52</v>
       </c>
+      <c r="R2" t="n">
+        <v>1.0329465864151928</v>
+      </c>
       <c r="S2" t="n">
+        <v>0.2384177725699285</v>
+      </c>
+      <c r="T2" t="n">
+        <v>230110.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -5313,13 +5313,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004221351128715135</v>
+        <v>0.0046002598319819015</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2856553126937284</v>
+        <v>0.34706010169049584</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -5334,37 +5334,37 @@
         <v>52</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003411522418330872</v>
+        <v>0.0042092316176365425</v>
       </c>
       <c r="P3" t="n">
-        <v>0.21594670513699074</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>350039.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.274439833417515</v>
+      </c>
+      <c r="Q3" t="s">
         <v>52</v>
       </c>
+      <c r="R3" t="n">
+        <v>1.0329465864151928</v>
+      </c>
       <c r="S3" t="n">
+        <v>0.2384177725699285</v>
+      </c>
+      <c r="T3" t="n">
+        <v>230110.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -5399,13 +5399,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.007410104487496083</v>
+        <v>-0.009041007452368148</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4162064798493882</v>
+        <v>0.6019512407109643</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -5420,37 +5420,37 @@
         <v>52</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00451998730545515</v>
+        <v>0.00558330109203913</v>
       </c>
       <c r="P4" t="n">
-        <v>0.10112916287179191</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>350039.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.1053853339718759</v>
+      </c>
+      <c r="Q4" t="s">
         <v>52</v>
       </c>
+      <c r="R4" t="n">
+        <v>1.0329465864151928</v>
+      </c>
       <c r="S4" t="n">
+        <v>0.2384177725699285</v>
+      </c>
+      <c r="T4" t="n">
+        <v>230110.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -5485,13 +5485,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0024276003051405875</v>
+        <v>0.00942981255770545</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07146203708729598</v>
+        <v>0.07373864673417062</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -5506,37 +5506,37 @@
         <v>52</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004823466937374072</v>
+        <v>0.005968898911116042</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6147610581965657</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>350039.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.11414844470560143</v>
+      </c>
+      <c r="Q5" t="s">
         <v>52</v>
       </c>
+      <c r="R5" t="n">
+        <v>1.0329465864151928</v>
+      </c>
       <c r="S5" t="n">
+        <v>0.2384177725699285</v>
+      </c>
+      <c r="T5" t="n">
+        <v>230110.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -5571,13 +5571,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006657255403560866</v>
+        <v>0.007230702191404411</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2554143966815126</v>
+        <v>0.30229890052583547</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -5592,37 +5592,37 @@
         <v>52</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003377170083501139</v>
+        <v>0.004167733793202915</v>
       </c>
       <c r="P6" t="n">
-        <v>0.04869577331431327</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>350039.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.08275557221158501</v>
+      </c>
+      <c r="Q6" t="s">
         <v>52</v>
       </c>
+      <c r="R6" t="n">
+        <v>1.0329465864151928</v>
+      </c>
       <c r="S6" t="n">
+        <v>0.2384177725699285</v>
+      </c>
+      <c r="T6" t="n">
+        <v>230110.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -5657,13 +5657,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.002390568292555957</v>
+        <v>0.004346984866169337</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07836126831581623</v>
+        <v>0.08111120768328191</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -5678,37 +5678,37 @@
         <v>52</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0046438607168498595</v>
+        <v>0.005745199260323331</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6067068360032342</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>350039.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.4492728852374015</v>
+      </c>
+      <c r="Q7" t="s">
         <v>52</v>
       </c>
+      <c r="R7" t="n">
+        <v>1.0329465864151928</v>
+      </c>
       <c r="S7" t="n">
+        <v>0.2384177725699285</v>
+      </c>
+      <c r="T7" t="n">
+        <v>230110.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -5837,13 +5837,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0038690963135752203</v>
+        <v>-0.004889142407402824</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38620414559441557</v>
+        <v>0.5424111495841875</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -5858,37 +5858,37 @@
         <v>53</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004023844871261818</v>
+        <v>0.0049622143374992754</v>
       </c>
       <c r="P2" t="n">
-        <v>0.33628032218182935</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>350975.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.32449037131474967</v>
+      </c>
+      <c r="Q2" t="s">
         <v>53</v>
       </c>
+      <c r="R2" t="n">
+        <v>2.645180257678123</v>
+      </c>
       <c r="S2" t="n">
+        <v>4.465543315182887</v>
+      </c>
+      <c r="T2" t="n">
+        <v>230753.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -5923,13 +5923,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002376815526289553</v>
+        <v>0.0015990157372289388</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28563287983474606</v>
+        <v>0.34706591030235795</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -5944,37 +5944,37 @@
         <v>53</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0034091825158449026</v>
+        <v>0.0042037485659807165</v>
       </c>
       <c r="P3" t="n">
-        <v>0.485690310790185</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>350975.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.7036647931799933</v>
+      </c>
+      <c r="Q3" t="s">
         <v>53</v>
       </c>
+      <c r="R3" t="n">
+        <v>2.645180257678123</v>
+      </c>
       <c r="S3" t="n">
+        <v>4.465543315182887</v>
+      </c>
+      <c r="T3" t="n">
+        <v>230753.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -6009,13 +6009,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0017787381903987731</v>
+        <v>6.141563695543588E-4</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161720920293468</v>
+        <v>0.601931502515677</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -6030,37 +6030,37 @@
         <v>53</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004516207786443735</v>
+        <v>0.005575091449627981</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6936871619733798</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>350975.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.912281969297668</v>
+      </c>
+      <c r="Q4" t="s">
         <v>53</v>
       </c>
+      <c r="R4" t="n">
+        <v>2.645180257678123</v>
+      </c>
       <c r="S4" t="n">
+        <v>4.465543315182887</v>
+      </c>
+      <c r="T4" t="n">
+        <v>230753.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -6095,13 +6095,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0014018026608490608</v>
+        <v>0.0038987490000766956</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07144098582520123</v>
+        <v>0.07371735145371891</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -6116,37 +6116,37 @@
         <v>53</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004820797855989508</v>
+        <v>0.005961597289948417</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7712179994417725</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>350975.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.5131271145719334</v>
+      </c>
+      <c r="Q5" t="s">
         <v>53</v>
       </c>
+      <c r="R5" t="n">
+        <v>2.645180257678123</v>
+      </c>
       <c r="S5" t="n">
+        <v>4.465543315182887</v>
+      </c>
+      <c r="T5" t="n">
+        <v>230753.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -6181,13 +6181,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>5.780395479382013E-4</v>
+        <v>9.766288572087647E-5</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2553714652040744</v>
+        <v>0.30224092427834093</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -6202,37 +6202,37 @@
         <v>53</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0033749057604561977</v>
+        <v>0.004162365294293717</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8640070385333598</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>350975.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.9812807215470558</v>
+      </c>
+      <c r="Q6" t="s">
         <v>53</v>
       </c>
+      <c r="R6" t="n">
+        <v>2.645180257678123</v>
+      </c>
       <c r="S6" t="n">
+        <v>4.465543315182887</v>
+      </c>
+      <c r="T6" t="n">
+        <v>230753.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -6267,13 +6267,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001989965957543396</v>
+        <v>0.0038853822016111793</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0783275162048579</v>
+        <v>0.08108453627905163</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -6288,37 +6288,37 @@
         <v>53</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004641547433226485</v>
+        <v>0.005738438547888321</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6681207217510524</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>350975.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.49835585106873526</v>
+      </c>
+      <c r="Q7" t="s">
         <v>53</v>
       </c>
+      <c r="R7" t="n">
+        <v>2.645180257678123</v>
+      </c>
       <c r="S7" t="n">
+        <v>4.465543315182887</v>
+      </c>
+      <c r="T7" t="n">
+        <v>230753.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -6447,13 +6447,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>9.376095324920829E-4</v>
+        <v>0.0026756205818197843</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3863922286237116</v>
+        <v>0.5428559762637123</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -6468,37 +6468,37 @@
         <v>54</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004513283631340966</v>
+        <v>0.005564985240484393</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8354286759956555</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>279796.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.6306623294628775</v>
+      </c>
+      <c r="Q2" t="s">
         <v>54</v>
       </c>
+      <c r="R2" t="n">
+        <v>44.17843699812178</v>
+      </c>
       <c r="S2" t="n">
+        <v>49.493393975400714</v>
+      </c>
+      <c r="T2" t="n">
+        <v>183685.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -6533,13 +6533,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0019131810694534394</v>
+        <v>-0.006284666265631155</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28564203919998854</v>
+        <v>0.34687644608977325</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -6554,37 +6554,37 @@
         <v>54</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0038215938171244743</v>
+        <v>0.004712992853953778</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6166362568982493</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>279796.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.18237706300202736</v>
+      </c>
+      <c r="Q3" t="s">
         <v>54</v>
       </c>
+      <c r="R3" t="n">
+        <v>44.17843699812178</v>
+      </c>
       <c r="S3" t="n">
+        <v>49.493393975400714</v>
+      </c>
+      <c r="T3" t="n">
+        <v>183685.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -6619,13 +6619,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>3.616398040624297E-5</v>
+        <v>0.004020196535178995</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4160906517605684</v>
+        <v>0.6018455508070882</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -6640,37 +6640,37 @@
         <v>54</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005060575174380083</v>
+        <v>0.0062535128731321145</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9942981955107479</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>279796.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.5203091854673492</v>
+      </c>
+      <c r="Q4" t="s">
         <v>54</v>
       </c>
+      <c r="R4" t="n">
+        <v>44.17843699812178</v>
+      </c>
       <c r="S4" t="n">
+        <v>49.493393975400714</v>
+      </c>
+      <c r="T4" t="n">
+        <v>183685.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -6705,13 +6705,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0038123620445664193</v>
+        <v>-0.00716955919206414</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07131803170881643</v>
+        <v>0.07348449791763073</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -6726,37 +6726,37 @@
         <v>54</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005407966097689434</v>
+        <v>0.006692419044882689</v>
       </c>
       <c r="P5" t="n">
-        <v>0.48084005861270707</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>279796.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.28403793749038236</v>
+      </c>
+      <c r="Q5" t="s">
         <v>54</v>
       </c>
+      <c r="R5" t="n">
+        <v>44.17843699812178</v>
+      </c>
       <c r="S5" t="n">
+        <v>49.493393975400714</v>
+      </c>
+      <c r="T5" t="n">
+        <v>183685.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -6791,13 +6791,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-5.458104459678437E-4</v>
+        <v>-0.001735134227337888</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25526812391885517</v>
+        <v>0.3022701908157988</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -6812,37 +6812,37 @@
         <v>54</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0037831049092283955</v>
+        <v>0.0046669222802498906</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8852827996961675</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>279796.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.7100465764083344</v>
+      </c>
+      <c r="Q6" t="s">
         <v>54</v>
       </c>
+      <c r="R6" t="n">
+        <v>44.17843699812178</v>
+      </c>
       <c r="S6" t="n">
+        <v>49.493393975400714</v>
+      </c>
+      <c r="T6" t="n">
+        <v>183685.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -6877,13 +6877,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004508552375268015</v>
+        <v>0.006123107797323358</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07824450671203305</v>
+        <v>0.08089392165936249</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -6898,37 +6898,37 @@
         <v>54</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005205342617545942</v>
+        <v>0.006439734537771445</v>
       </c>
       <c r="P7" t="n">
-        <v>0.38641445902047256</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>279796.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.34169074884871986</v>
+      </c>
+      <c r="Q7" t="s">
         <v>54</v>
       </c>
+      <c r="R7" t="n">
+        <v>44.17843699812178</v>
+      </c>
       <c r="S7" t="n">
+        <v>49.493393975400714</v>
+      </c>
+      <c r="T7" t="n">
+        <v>183685.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
